--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
   <si>
     <t>序号</t>
   </si>
@@ -225,7 +225,19 @@
     <t>能量值道具</t>
   </si>
   <si>
+    <t>主线任务</t>
+  </si>
+  <si>
+    <t>6001_6090_6091</t>
+  </si>
+  <si>
     <t>雇员抽卡</t>
+  </si>
+  <si>
+    <t>联盟任务</t>
+  </si>
+  <si>
+    <t>6011_6090_6091</t>
   </si>
   <si>
     <t>联盟引导</t>
@@ -1053,16 +1065,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>43815</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>52070</xdr:rowOff>
+      <xdr:rowOff>153035</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>708025</xdr:colOff>
+      <xdr:colOff>192405</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>16510</xdr:rowOff>
+      <xdr:rowOff>117475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1079,7 +1091,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10288905" y="1068070"/>
+          <a:off x="9773285" y="1169035"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1346,7 +1358,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
@@ -1544,7 +1556,7 @@
         <v>601</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C10" s="20"/>
       <c r="D10" s="20">
@@ -1556,33 +1568,59 @@
       <c r="F10" s="20">
         <v>1024014</v>
       </c>
-      <c r="G10" s="21"/>
+      <c r="G10" s="21" t="s">
+        <v>22</v>
+      </c>
       <c r="H10" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:8">
-      <c r="A11" s="14">
+      <c r="A11" s="20">
+        <v>602</v>
+      </c>
+      <c r="B11" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20">
+        <v>601</v>
+      </c>
+      <c r="E11" s="20">
+        <v>6</v>
+      </c>
+      <c r="F11" s="20">
+        <v>1024014</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:8">
+      <c r="A12" s="14">
         <v>701</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B12" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14">
+      <c r="C12" s="14"/>
+      <c r="D12" s="14">
         <v>701</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E12" s="14">
         <v>7</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="4" t="s">
-        <v>22</v>
+      <c r="F12" s="14"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="9:9">
-      <c r="I19" s="1"/>
+    <row r="20" customHeight="1" spans="9:9">
+      <c r="I20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
   <si>
     <t>序号</t>
   </si>
@@ -210,37 +210,55 @@
     <t>GuideIdList</t>
   </si>
   <si>
+    <t>创建新号</t>
+  </si>
+  <si>
     <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014</t>
   </si>
   <si>
     <t>新手开场引导</t>
   </si>
   <si>
+    <t>经营大厅界面</t>
+  </si>
+  <si>
+    <t>成就勋章</t>
+  </si>
+  <si>
+    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612_1613_1614_1615</t>
+  </si>
+  <si>
+    <t>测试用</t>
+  </si>
+  <si>
+    <t>拜访</t>
+  </si>
+  <si>
+    <t>SLOT游戏中</t>
+  </si>
+  <si>
+    <t>能量值道具</t>
+  </si>
+  <si>
+    <t>主线任务界面</t>
+  </si>
+  <si>
+    <t>6001_6090_6091</t>
+  </si>
+  <si>
+    <t>雇员抽卡</t>
+  </si>
+  <si>
+    <t>联盟任务界面</t>
+  </si>
+  <si>
+    <t>6011_6090_6091</t>
+  </si>
+  <si>
     <t>经营大厅</t>
   </si>
   <si>
-    <t>SLOT游戏中</t>
-  </si>
-  <si>
-    <t>能量值道具</t>
-  </si>
-  <si>
-    <t>主线任务</t>
-  </si>
-  <si>
-    <t>6001_6090_6091</t>
-  </si>
-  <si>
-    <t>雇员抽卡</t>
-  </si>
-  <si>
-    <t>联盟任务</t>
-  </si>
-  <si>
-    <t>6011_6090_6091</t>
-  </si>
-  <si>
-    <t>联盟引导</t>
+    <t>赛季</t>
   </si>
 </sst>
 </file>
@@ -253,7 +271,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -271,6 +289,12 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -803,137 +827,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="38" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -946,7 +970,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -964,16 +991,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -982,22 +1009,31 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1361,38 +1397,38 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.975" style="3" customWidth="1"/>
-    <col min="3" max="3" width="10.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="15.4333333333333" style="3" customWidth="1"/>
-    <col min="6" max="6" width="12.35" style="3" customWidth="1"/>
-    <col min="7" max="7" width="41.3166666666667" style="3" customWidth="1"/>
-    <col min="8" max="8" width="14.5583333333333" style="4" customWidth="1"/>
-    <col min="9" max="9" width="6.31666666666667" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="15.625" style="3"/>
+    <col min="1" max="1" width="5.875" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.975" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.75" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.4333333333333" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.35" style="4" customWidth="1"/>
+    <col min="7" max="7" width="41.3166666666667" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.5583333333333" style="5" customWidth="1"/>
+    <col min="9" max="9" width="6.31666666666667" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="15.625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -1400,223 +1436,236 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="7"/>
+      <c r="H2" s="8"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="7"/>
+      <c r="H3" s="8"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="H4" s="9"/>
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="H4" s="10"/>
     </row>
     <row r="5" customHeight="1" spans="1:8">
-      <c r="A5" s="10">
+      <c r="A5" s="11">
         <v>101</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10">
+      <c r="B5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11">
         <v>101</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="11">
         <v>1</v>
       </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="F5" s="11"/>
+      <c r="G5" s="12" t="s">
         <v>17</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:8">
-      <c r="A6" s="12">
+      <c r="A6" s="13">
         <v>201</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12">
+      <c r="B6" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13">
         <v>201</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <v>2</v>
       </c>
-      <c r="F6" s="12">
-        <v>100020002</v>
-      </c>
-      <c r="G6" s="13"/>
+      <c r="F6" s="13">
+        <v>1150001</v>
+      </c>
+      <c r="G6" s="14"/>
+      <c r="H6" s="5" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="7" customHeight="1" spans="1:8">
-      <c r="A7" s="14">
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:8">
+      <c r="A7" s="15">
         <v>301</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14">
+      <c r="B7" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15">
         <v>301</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="15">
         <v>3</v>
       </c>
-      <c r="F7" s="14">
-        <v>5</v>
-      </c>
-      <c r="G7" s="15"/>
+      <c r="F7" s="15">
+        <v>2</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="8" customHeight="1" spans="1:8">
-      <c r="A8" s="16">
+      <c r="A8" s="18">
         <v>401</v>
       </c>
-      <c r="B8" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16">
+      <c r="B8" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18">
         <v>401</v>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="18">
         <v>4</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="18">
         <v>10</v>
       </c>
-      <c r="G8" s="17"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="5" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="9" customHeight="1" spans="1:8">
-      <c r="A9" s="18">
+      <c r="A9" s="20">
         <v>501</v>
       </c>
-      <c r="B9" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18">
+      <c r="B9" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20">
         <v>501</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="20">
         <v>5</v>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="20">
         <v>1022502</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="4" t="s">
-        <v>20</v>
+      <c r="G9" s="21"/>
+      <c r="H9" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="1:8">
-      <c r="A10" s="20">
+      <c r="A10" s="22">
         <v>601</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20">
+      <c r="B10" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22">
         <v>601</v>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="22">
         <v>6</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="22">
         <v>1024014</v>
       </c>
-      <c r="G10" s="21" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>23</v>
+      <c r="G10" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:8">
-      <c r="A11" s="20">
+      <c r="A11" s="22">
         <v>602</v>
       </c>
-      <c r="B11" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" s="20"/>
-      <c r="D11" s="20">
+      <c r="B11" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="22"/>
+      <c r="D11" s="22">
         <v>601</v>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="22">
         <v>6</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="22">
         <v>1024014</v>
       </c>
-      <c r="G11" s="21" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>23</v>
+      <c r="G11" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:8">
-      <c r="A12" s="14">
+      <c r="A12" s="24">
         <v>701</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14">
+      <c r="B12" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24">
         <v>701</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="24">
         <v>7</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="4" t="s">
-        <v>26</v>
+      <c r="F12" s="24"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="5" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="9:9">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -213,7 +213,7 @@
     <t>创建新号</t>
   </si>
   <si>
-    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014</t>
+    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1841_1842_1843_1844_1845_1846_1847_1848_1849_1850_1851_1852_1853_1701_1702_1703_1704_1705_1706_1707_1708_1709_1861</t>
   </si>
   <si>
     <t>新手开场引导</t>
@@ -1102,15 +1102,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:colOff>110490</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>153035</xdr:rowOff>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>192405</xdr:colOff>
+      <xdr:colOff>293370</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>117475</xdr:rowOff>
+      <xdr:rowOff>27940</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1127,7 +1127,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9773285" y="1169035"/>
+          <a:off x="9874250" y="1079500"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>序号</t>
   </si>
@@ -183,6 +183,9 @@
     <t>引导列表ID</t>
   </si>
   <si>
+    <t>跳过引导ID</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -210,10 +213,16 @@
     <t>GuideIdList</t>
   </si>
   <si>
+    <t>SkipGuideId</t>
+  </si>
+  <si>
     <t>创建新号</t>
   </si>
   <si>
-    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1841_1842_1843_1844_1845_1846_1847_1848_1849_1850_1851_1852_1853_1701_1702_1703_1704_1705_1706_1707_1708_1709_1861</t>
+    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1841_1841_1842_1843_1844_1845_1846_1847_1848_1849_1850_1851_1852_1853_1601_1602_1603_1604_1605_1606_1607_1608_1609_1610</t>
+  </si>
+  <si>
+    <t>1004_1846</t>
   </si>
   <si>
     <t>新手开场引导</t>
@@ -223,9 +232,6 @@
   </si>
   <si>
     <t>成就勋章</t>
-  </si>
-  <si>
-    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612_1613_1614_1615</t>
   </si>
   <si>
     <t>测试用</t>
@@ -957,7 +963,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -980,6 +986,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1101,13 +1110,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>110490</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
+      <xdr:col>17</xdr:col>
       <xdr:colOff>293370</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>27940</xdr:rowOff>
@@ -1127,7 +1136,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9874250" y="1079500"/>
+          <a:off x="12560300" y="1079500"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1394,7 +1403,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="4" customWidth="1"/>
@@ -1404,12 +1413,13 @@
     <col min="5" max="5" width="15.4333333333333" style="4" customWidth="1"/>
     <col min="6" max="6" width="12.35" style="4" customWidth="1"/>
     <col min="7" max="7" width="41.3166666666667" style="4" customWidth="1"/>
-    <col min="8" max="8" width="14.5583333333333" style="5" customWidth="1"/>
-    <col min="9" max="9" width="6.31666666666667" style="4" customWidth="1"/>
-    <col min="10" max="16384" width="15.625" style="4"/>
+    <col min="8" max="8" width="35.25" style="4" customWidth="1"/>
+    <col min="9" max="9" width="14.5583333333333" style="5" customWidth="1"/>
+    <col min="10" max="10" width="6.31666666666667" style="4" customWidth="1"/>
+    <col min="11" max="16384" width="15.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1431,245 +1441,262 @@
       <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:8">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="9"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:8">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
       <c r="A3" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="8"/>
+        <v>16</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="9"/>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="H4" s="10"/>
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="I4" s="11"/>
     </row>
-    <row r="5" customHeight="1" spans="1:8">
-      <c r="A5" s="11">
+    <row r="5" customHeight="1" spans="1:9">
+      <c r="A5" s="12">
         <v>101</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11">
+      <c r="B5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12">
         <v>101</v>
       </c>
-      <c r="E5" s="11">
+      <c r="E5" s="12">
         <v>1</v>
       </c>
-      <c r="F5" s="11"/>
-      <c r="G5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>18</v>
+      <c r="F5" s="12"/>
+      <c r="G5" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
-    <row r="6" customHeight="1" spans="1:8">
-      <c r="A6" s="13">
+    <row r="6" customHeight="1" spans="1:9">
+      <c r="A6" s="14">
         <v>201</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13">
+      <c r="B6" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14">
         <v>201</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <v>2</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <v>1150001</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="5" t="s">
-        <v>20</v>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:8">
-      <c r="A7" s="15">
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A7" s="16">
         <v>301</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15">
+      <c r="B7" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16">
         <v>301</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="16">
         <v>3</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="16">
         <v>2</v>
       </c>
-      <c r="G7" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H7" s="17" t="s">
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:9">
+      <c r="A8" s="19">
+        <v>401</v>
+      </c>
+      <c r="B8" s="19" t="s">
         <v>22</v>
       </c>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19">
+        <v>401</v>
+      </c>
+      <c r="E8" s="19">
+        <v>4</v>
+      </c>
+      <c r="F8" s="19">
+        <v>10</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="5" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="8" customHeight="1" spans="1:8">
-      <c r="A8" s="18">
-        <v>401</v>
-      </c>
-      <c r="B8" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18">
-        <v>401</v>
-      </c>
-      <c r="E8" s="18">
-        <v>4</v>
-      </c>
-      <c r="F8" s="18">
-        <v>10</v>
-      </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="5" t="s">
-        <v>23</v>
+    <row r="9" customHeight="1" spans="1:9">
+      <c r="A9" s="21">
+        <v>501</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21">
+        <v>501</v>
+      </c>
+      <c r="E9" s="21">
+        <v>5</v>
+      </c>
+      <c r="F9" s="21">
+        <v>1022502</v>
+      </c>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:8">
-      <c r="A9" s="20">
-        <v>501</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20">
-        <v>501</v>
-      </c>
-      <c r="E9" s="20">
-        <v>5</v>
-      </c>
-      <c r="F9" s="20">
-        <v>1022502</v>
-      </c>
-      <c r="G9" s="21"/>
-      <c r="H9" s="5" t="s">
-        <v>25</v>
+    <row r="10" customHeight="1" spans="1:9">
+      <c r="A10" s="23">
+        <v>601</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23">
+        <v>601</v>
+      </c>
+      <c r="E10" s="23">
+        <v>6</v>
+      </c>
+      <c r="F10" s="23">
+        <v>1024014</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="24"/>
+      <c r="I10" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:8">
-      <c r="A10" s="22">
+    <row r="11" customHeight="1" spans="1:9">
+      <c r="A11" s="23">
+        <v>602</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23">
         <v>601</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22">
-        <v>601</v>
-      </c>
-      <c r="E10" s="22">
+      <c r="E11" s="23">
         <v>6</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F11" s="23">
         <v>1024014</v>
       </c>
-      <c r="G10" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>28</v>
+      <c r="G11" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="24"/>
+      <c r="I11" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:8">
-      <c r="A11" s="22">
-        <v>602</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22">
-        <v>601</v>
-      </c>
-      <c r="E11" s="22">
-        <v>6</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1024014</v>
-      </c>
-      <c r="G11" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>28</v>
+    <row r="12" customHeight="1" spans="1:9">
+      <c r="A12" s="25">
+        <v>701</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25">
+        <v>701</v>
+      </c>
+      <c r="E12" s="25">
+        <v>7</v>
+      </c>
+      <c r="F12" s="25"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:8">
-      <c r="A12" s="24">
-        <v>701</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24">
-        <v>701</v>
-      </c>
-      <c r="E12" s="24">
-        <v>7</v>
-      </c>
-      <c r="F12" s="24"/>
-      <c r="G12" s="25"/>
-      <c r="H12" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="9:9">
-      <c r="I20" s="1"/>
+    <row r="20" customHeight="1" spans="10:10">
+      <c r="J20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -72,8 +72,9 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-必填写：触发时的界面名称
-</t>
+选填写项：
+1. 经营大厅
+2. SLOT游戏</t>
         </r>
       </text>
     </comment>
@@ -95,6 +96,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+必填写项：
 1. 创建新号-首次进入经营大厅
 2. 任务ID触发(领取任务奖励后且回到了经营大厅)
 3. 经营等级触发(回到经营大厅)
@@ -102,7 +104,7 @@
 5. 道具不足触发(道具不足)
 6. 获得指定道具ID触发
 7. 功能解锁触发(回到经营大厅 填写功能ID，GameFunction.xlsx 表中ID )
-</t>
+8.  引导组触发(填写的引导组完成后触发) </t>
         </r>
       </text>
     </comment>
@@ -124,6 +126,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+选填写项：
 根据触发条件而分类填写的参数
 解发条件1：不填写
 触发条件2：填写任务ID
@@ -160,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
   <si>
     <t>序号</t>
   </si>
@@ -183,7 +186,7 @@
     <t>引导列表ID</t>
   </si>
   <si>
-    <t>跳过引导ID</t>
+    <t>跳过奖励界面引导ID</t>
   </si>
   <si>
     <t>int</t>
@@ -219,49 +222,73 @@
     <t>创建新号</t>
   </si>
   <si>
-    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014_1841_1841_1842_1843_1844_1845_1846_1847_1848_1849_1850_1851_1852_1853_1601_1602_1603_1604_1605_1606_1607_1608_1609_1610</t>
-  </si>
-  <si>
-    <t>1004_1846</t>
+    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014</t>
   </si>
   <si>
     <t>新手开场引导</t>
   </si>
   <si>
+    <t>1841_1841_1842_1843_1844_1845_1846_1847_1848_1849_1850_1851_1852_1853</t>
+  </si>
+  <si>
+    <t>解锁雇员&amp;雇员升级</t>
+  </si>
+  <si>
     <t>经营大厅界面</t>
   </si>
   <si>
-    <t>成就勋章</t>
-  </si>
-  <si>
-    <t>测试用</t>
-  </si>
-  <si>
-    <t>拜访</t>
-  </si>
-  <si>
-    <t>SLOT游戏中</t>
-  </si>
-  <si>
-    <t>能量值道具</t>
-  </si>
-  <si>
-    <t>主线任务界面</t>
-  </si>
-  <si>
-    <t>6001_6090_6091</t>
-  </si>
-  <si>
-    <t>雇员抽卡</t>
-  </si>
-  <si>
-    <t>联盟任务界面</t>
-  </si>
-  <si>
-    <t>6011_6090_6091</t>
-  </si>
-  <si>
-    <t>经营大厅</t>
+    <t>1861_1862_1863_1864_1865</t>
+  </si>
+  <si>
+    <t>解锁联盟&amp;加入联盟</t>
+  </si>
+  <si>
+    <t>1201_1202_1203_1204_1205_1206_1207_1208_1209_1210_1211</t>
+  </si>
+  <si>
+    <t>试玩[超级明星]-默认解锁</t>
+  </si>
+  <si>
+    <t>1301_1302_1303_1304_1305_1306_1307</t>
+  </si>
+  <si>
+    <t>主线任务第1次引导</t>
+  </si>
+  <si>
+    <t>1401_1402_1403_1404_1405_1406_1407_1408_1409_1410_1411_1412_1413_1414_1415_1416_1417_1418_1419_1420_1421</t>
+  </si>
+  <si>
+    <t>研究院-SLOT升级词条-超级明星-解锁投注底数</t>
+  </si>
+  <si>
+    <t>1501_1502_1503_1504_1505_1506_1507</t>
+  </si>
+  <si>
+    <t>主线任务第2次引导</t>
+  </si>
+  <si>
+    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612_1613_1614_1615</t>
+  </si>
+  <si>
+    <t>研究院升级-解锁第2个游戏【麻将胡了】</t>
+  </si>
+  <si>
+    <t>1701_1702_1703_1704_1705_1706_1707_1708_1709</t>
+  </si>
+  <si>
+    <t>解锁捕鱼机台建筑-1110</t>
+  </si>
+  <si>
+    <t>1801_1802_1803_1804_1805_1806_1807_1808_1809_1810</t>
+  </si>
+  <si>
+    <t>解锁游客&amp;游客升星</t>
+  </si>
+  <si>
+    <t>1821_1822_1823_1824_1825_1826_1827</t>
+  </si>
+  <si>
+    <t>主线任务第3次引导</t>
   </si>
   <si>
     <t>赛季</t>
@@ -277,7 +304,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -287,30 +314,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
@@ -322,6 +325,11 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -477,7 +485,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -487,36 +495,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -833,217 +811,175 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="37" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="38" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1110,16 +1046,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>110490</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>120015</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>29210</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>293370</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>27940</xdr:rowOff>
+      <xdr:colOff>784225</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>247650</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1136,7 +1072,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12560300" y="1079500"/>
+          <a:off x="15110460" y="1045210"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1403,45 +1339,45 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="13.975" style="4" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="4" customWidth="1"/>
     <col min="3" max="3" width="10.75" style="4" customWidth="1"/>
     <col min="4" max="4" width="13.875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="15.4333333333333" style="4" customWidth="1"/>
-    <col min="6" max="6" width="12.35" style="4" customWidth="1"/>
-    <col min="7" max="7" width="41.3166666666667" style="4" customWidth="1"/>
-    <col min="8" max="8" width="35.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.5583333333333" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="4" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="4" customWidth="1"/>
+    <col min="7" max="7" width="83.125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="20.2833333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="23.5" style="4" customWidth="1"/>
     <col min="10" max="10" width="6.31666666666667" style="4" customWidth="1"/>
     <col min="11" max="16384" width="15.625" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1449,254 +1385,379 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="9"/>
+      <c r="I2" s="6"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="9"/>
+      <c r="I3" s="6"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="I4" s="11"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
     </row>
     <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="12">
+      <c r="A5" s="7">
         <v>101</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12">
+      <c r="C5" s="7"/>
+      <c r="D5" s="7">
         <v>101</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="7">
         <v>1</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="8">
+        <v>1004</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="5" t="s">
+    </row>
+    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A6" s="9">
+        <v>201</v>
+      </c>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9">
+        <v>201</v>
+      </c>
+      <c r="E6" s="9">
+        <v>8</v>
+      </c>
+      <c r="F6" s="9">
+        <v>101</v>
+      </c>
+      <c r="G6" s="10" t="s">
         <v>21</v>
       </c>
+      <c r="H6" s="10">
+        <v>1846</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="6" customHeight="1" spans="1:9">
-      <c r="A6" s="14">
-        <v>201</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14">
-        <v>201</v>
-      </c>
-      <c r="E6" s="14">
-        <v>2</v>
-      </c>
-      <c r="F6" s="14">
-        <v>1150001</v>
-      </c>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="5" t="s">
+    <row r="7" s="4" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A7" s="11">
+        <v>301</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>23</v>
       </c>
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11">
+        <v>301</v>
+      </c>
+      <c r="E7" s="11">
+        <v>4</v>
+      </c>
+      <c r="F7" s="11">
+        <v>3</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H7" s="4"/>
+      <c r="I7" s="11" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A7" s="16">
-        <v>301</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16">
-        <v>301</v>
-      </c>
-      <c r="E7" s="16">
-        <v>3</v>
-      </c>
-      <c r="F7" s="16">
-        <v>2</v>
-      </c>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:9">
-      <c r="A8" s="19">
+    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A8" s="12">
         <v>401</v>
       </c>
-      <c r="B8" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19">
+      <c r="B8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="12">
+        <v>1</v>
+      </c>
+      <c r="D8" s="12">
         <v>401</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="12">
         <v>4</v>
       </c>
-      <c r="F8" s="19">
-        <v>10</v>
-      </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-      <c r="I8" s="5" t="s">
-        <v>25</v>
+      <c r="F8" s="12">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:9">
-      <c r="A9" s="21">
+      <c r="A9" s="11">
         <v>501</v>
       </c>
-      <c r="B9" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21">
+      <c r="B9" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="11">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11">
         <v>501</v>
       </c>
-      <c r="E9" s="21">
-        <v>5</v>
-      </c>
-      <c r="F9" s="21">
-        <v>1022502</v>
-      </c>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="5" t="s">
-        <v>27</v>
+      <c r="E9" s="11">
+        <v>4</v>
+      </c>
+      <c r="F9" s="11">
+        <v>8</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:9">
-      <c r="A10" s="23">
-        <v>601</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23">
-        <v>601</v>
-      </c>
-      <c r="E10" s="23">
-        <v>6</v>
-      </c>
-      <c r="F10" s="23">
-        <v>1024014</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="24"/>
-      <c r="I10" s="5" t="s">
+    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A10" s="12">
+        <v>1001</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C10" s="12">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12">
+        <v>1001</v>
+      </c>
+      <c r="E10" s="12">
+        <v>4</v>
+      </c>
+      <c r="F10" s="12">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>30</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="12" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="23">
-        <v>602</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23">
-        <v>601</v>
-      </c>
-      <c r="E11" s="23">
-        <v>6</v>
-      </c>
-      <c r="F11" s="23">
-        <v>1024014</v>
-      </c>
-      <c r="G11" s="24" t="s">
+      <c r="A11" s="11">
+        <v>1011</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11">
+        <v>1011</v>
+      </c>
+      <c r="E11" s="11">
+        <v>4</v>
+      </c>
+      <c r="F11" s="11">
+        <v>12</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H11" s="24"/>
-      <c r="I11" s="5" t="s">
-        <v>30</v>
+      <c r="I11" s="11" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:9">
-      <c r="A12" s="25">
-        <v>701</v>
-      </c>
-      <c r="B12" s="25" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25">
-        <v>701</v>
-      </c>
-      <c r="E12" s="25">
-        <v>7</v>
-      </c>
-      <c r="F12" s="25"/>
-      <c r="G12" s="26"/>
-      <c r="H12" s="26"/>
-      <c r="I12" s="5" t="s">
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A12" s="12">
+        <v>1021</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="12">
+        <v>1021</v>
+      </c>
+      <c r="E12" s="12">
+        <v>4</v>
+      </c>
+      <c r="F12" s="12">
+        <v>14</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="12" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="20" customHeight="1" spans="10:10">
-      <c r="J20" s="1"/>
+    <row r="13" customHeight="1" spans="1:9">
+      <c r="A13" s="11">
+        <v>1031</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="11">
+        <v>1</v>
+      </c>
+      <c r="D13" s="11">
+        <v>1031</v>
+      </c>
+      <c r="E13" s="11">
+        <v>4</v>
+      </c>
+      <c r="F13" s="11">
+        <v>16</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" s="3" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A14" s="12">
+        <v>1041</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="12">
+        <v>1</v>
+      </c>
+      <c r="D14" s="12">
+        <v>1041</v>
+      </c>
+      <c r="E14" s="12">
+        <v>4</v>
+      </c>
+      <c r="F14" s="12">
+        <v>18</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:9">
+      <c r="A15" s="11">
+        <v>1051</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="11">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11">
+        <v>1051</v>
+      </c>
+      <c r="E15" s="11">
+        <v>4</v>
+      </c>
+      <c r="F15" s="11">
+        <v>20</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:9">
+      <c r="A16" s="12">
+        <v>1061</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12">
+        <v>1061</v>
+      </c>
+      <c r="E16" s="12">
+        <v>4</v>
+      </c>
+      <c r="F16" s="12">
+        <v>22</v>
+      </c>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="10:10">
+      <c r="J24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>序号</t>
   </si>
@@ -183,7 +183,10 @@
     <t>引导列表ID</t>
   </si>
   <si>
-    <t>跳过引导ID</t>
+    <t>跳过奖励界面引导ID</t>
+  </si>
+  <si>
+    <t>跳过清CD界面引导ID</t>
   </si>
   <si>
     <t>int</t>
@@ -1110,13 +1113,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>110490</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>293370</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>27940</xdr:rowOff>
@@ -1136,7 +1139,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12560300" y="1079500"/>
+          <a:off x="13100050" y="1079500"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1403,7 +1406,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="4" customWidth="1"/>
@@ -1413,13 +1416,14 @@
     <col min="5" max="5" width="15.4333333333333" style="4" customWidth="1"/>
     <col min="6" max="6" width="12.35" style="4" customWidth="1"/>
     <col min="7" max="7" width="41.3166666666667" style="4" customWidth="1"/>
-    <col min="8" max="8" width="35.25" style="4" customWidth="1"/>
-    <col min="9" max="9" width="14.5583333333333" style="5" customWidth="1"/>
-    <col min="10" max="10" width="6.31666666666667" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="15.625" style="4"/>
+    <col min="8" max="8" width="20.2833333333333" style="4" customWidth="1"/>
+    <col min="9" max="9" width="22.05" style="4" customWidth="1"/>
+    <col min="10" max="10" width="14.5583333333333" style="5" customWidth="1"/>
+    <col min="11" max="11" width="6.31666666666667" style="4" customWidth="1"/>
+    <col min="12" max="16384" width="15.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1444,75 +1448,80 @@
       <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="9"/>
+        <v>11</v>
+      </c>
+      <c r="I2" s="8"/>
+      <c r="J2" s="9"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
       <c r="A3" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="9"/>
+        <v>18</v>
+      </c>
+      <c r="I3" s="8"/>
+      <c r="J3" s="9"/>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:9">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:10">
       <c r="A4" s="10"/>
       <c r="B4" s="10"/>
       <c r="C4" s="10"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
-      <c r="I4" s="11"/>
+      <c r="J4" s="11"/>
     </row>
-    <row r="5" customHeight="1" spans="1:9">
+    <row r="5" customHeight="1" spans="1:10">
       <c r="A5" s="12">
         <v>101</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12">
@@ -1523,21 +1532,22 @@
       </c>
       <c r="F5" s="12"/>
       <c r="G5" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="I5" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="5" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="6" customHeight="1" spans="1:9">
+    <row r="6" customHeight="1" spans="1:10">
       <c r="A6" s="14">
         <v>201</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" s="14"/>
       <c r="D6" s="14">
@@ -1551,16 +1561,17 @@
       </c>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
-      <c r="I6" s="5" t="s">
-        <v>23</v>
+      <c r="I6" s="15"/>
+      <c r="J6" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:9">
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A7" s="16">
         <v>301</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16">
@@ -1574,16 +1585,17 @@
       </c>
       <c r="G7" s="17"/>
       <c r="H7" s="17"/>
-      <c r="I7" s="18" t="s">
-        <v>24</v>
+      <c r="I7" s="17"/>
+      <c r="J7" s="18" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="1:9">
+    <row r="8" customHeight="1" spans="1:10">
       <c r="A8" s="19">
         <v>401</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="19"/>
       <c r="D8" s="19">
@@ -1597,16 +1609,17 @@
       </c>
       <c r="G8" s="20"/>
       <c r="H8" s="20"/>
-      <c r="I8" s="5" t="s">
-        <v>25</v>
+      <c r="I8" s="20"/>
+      <c r="J8" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:9">
+    <row r="9" customHeight="1" spans="1:10">
       <c r="A9" s="21">
         <v>501</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21">
@@ -1620,16 +1633,17 @@
       </c>
       <c r="G9" s="22"/>
       <c r="H9" s="22"/>
-      <c r="I9" s="5" t="s">
-        <v>27</v>
+      <c r="I9" s="22"/>
+      <c r="J9" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="1:9">
+    <row r="10" customHeight="1" spans="1:10">
       <c r="A10" s="23">
         <v>601</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23">
@@ -1642,19 +1656,20 @@
         <v>1024014</v>
       </c>
       <c r="G10" s="24" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H10" s="24"/>
-      <c r="I10" s="5" t="s">
-        <v>30</v>
+      <c r="I10" s="24"/>
+      <c r="J10" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:9">
+    <row r="11" customHeight="1" spans="1:10">
       <c r="A11" s="23">
         <v>602</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="23"/>
       <c r="D11" s="23">
@@ -1667,19 +1682,20 @@
         <v>1024014</v>
       </c>
       <c r="G11" s="24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H11" s="24"/>
-      <c r="I11" s="5" t="s">
-        <v>30</v>
+      <c r="I11" s="24"/>
+      <c r="J11" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:9">
+    <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="25">
         <v>701</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="25"/>
       <c r="D12" s="25">
@@ -1691,12 +1707,13 @@
       <c r="F12" s="25"/>
       <c r="G12" s="26"/>
       <c r="H12" s="26"/>
-      <c r="I12" s="5" t="s">
-        <v>34</v>
+      <c r="I12" s="26"/>
+      <c r="J12" s="5" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="20" customHeight="1" spans="10:10">
-      <c r="J20" s="1"/>
+    <row r="20" customHeight="1" spans="11:11">
+      <c r="K20" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="24045" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
   <si>
     <t>序号</t>
   </si>
@@ -189,6 +189,9 @@
     <t>跳过奖励界面引导ID</t>
   </si>
   <si>
+    <t>是否开启</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -198,6 +201,9 @@
     <t>list&lt;int&gt;{_}</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
@@ -217,6 +223,9 @@
   </si>
   <si>
     <t>SkipGuideId</t>
+  </si>
+  <si>
+    <t>isOpen</t>
   </si>
   <si>
     <t>创建新号</t>
@@ -304,7 +313,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,6 +324,12 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -811,133 +826,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -957,28 +972,28 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1046,13 +1061,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>120015</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>29210</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>784225</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>247650</xdr:rowOff>
@@ -1072,7 +1087,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15110460" y="1045210"/>
+          <a:off x="16656050" y="1045210"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1339,425 +1354,470 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.75" style="4" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="4" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="4" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="4" customWidth="1"/>
-    <col min="7" max="7" width="83.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="20.2833333333333" style="4" customWidth="1"/>
-    <col min="9" max="9" width="23.5" style="4" customWidth="1"/>
-    <col min="10" max="10" width="6.31666666666667" style="4" customWidth="1"/>
-    <col min="11" max="16384" width="15.625" style="4"/>
+    <col min="1" max="1" width="5.875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="11.875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="10.75" style="5" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="5" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="5" customWidth="1"/>
+    <col min="7" max="7" width="83.125" style="5" customWidth="1"/>
+    <col min="8" max="9" width="20.2833333333333" style="5" customWidth="1"/>
+    <col min="10" max="10" width="23.5" style="5" customWidth="1"/>
+    <col min="11" max="11" width="6.31666666666667" style="5" customWidth="1"/>
+    <col min="12" max="16384" width="15.625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A2" s="5" t="s">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="7"/>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A3" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="J3" s="7"/>
+    </row>
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A5" s="8">
+        <v>101</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8">
+        <v>101</v>
+      </c>
+      <c r="E5" s="8">
+        <v>1</v>
+      </c>
+      <c r="F5" s="8"/>
+      <c r="G5" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="9">
+        <v>1004</v>
+      </c>
+      <c r="I5" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A6" s="8">
+        <v>201</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8">
+        <v>201</v>
+      </c>
+      <c r="E6" s="8">
         <v>8</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="F6" s="8">
+        <v>101</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H6" s="9">
+        <v>1846</v>
+      </c>
+      <c r="I6" s="9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A7" s="10">
+        <v>301</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10">
+        <v>301</v>
+      </c>
+      <c r="E7" s="10">
+        <v>3</v>
+      </c>
+      <c r="F7" s="10">
+        <v>3</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A8" s="11">
+        <v>401</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11">
+        <v>401</v>
+      </c>
+      <c r="E8" s="11">
+        <v>3</v>
+      </c>
+      <c r="F8" s="11">
+        <v>5</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:10">
+      <c r="A9" s="12">
+        <v>501</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="12">
+        <v>1</v>
+      </c>
+      <c r="D9" s="12">
+        <v>501</v>
+      </c>
+      <c r="E9" s="12">
+        <v>3</v>
+      </c>
+      <c r="F9" s="12">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="G9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="I9" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A10" s="11">
+        <v>1001</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="11">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11">
+        <v>1001</v>
+      </c>
+      <c r="E10" s="11">
+        <v>3</v>
+      </c>
+      <c r="F10" s="11">
         <v>10</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" s="6"/>
+      <c r="G10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>34</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+    <row r="11" customHeight="1" spans="1:10">
+      <c r="A11" s="12">
+        <v>1011</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="12">
+        <v>1</v>
+      </c>
+      <c r="D11" s="12">
+        <v>1011</v>
+      </c>
+      <c r="E11" s="12">
+        <v>3</v>
+      </c>
+      <c r="F11" s="12">
         <v>12</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="G11" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A12" s="11">
+        <v>1021</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1</v>
+      </c>
+      <c r="D12" s="11">
+        <v>1021</v>
+      </c>
+      <c r="E12" s="11">
+        <v>3</v>
+      </c>
+      <c r="F12" s="11">
         <v>14</v>
       </c>
-      <c r="F3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="G12" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="A13" s="12">
+        <v>1031</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C13" s="12">
+        <v>1</v>
+      </c>
+      <c r="D13" s="12">
+        <v>1031</v>
+      </c>
+      <c r="E13" s="12">
+        <v>3</v>
+      </c>
+      <c r="F13" s="12">
         <v>16</v>
       </c>
-      <c r="H3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="I3" s="6"/>
+      <c r="G13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="I13" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="12" t="s">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A14" s="11">
+        <v>1041</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="11">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11">
+        <v>1041</v>
+      </c>
+      <c r="E14" s="11">
+        <v>3</v>
+      </c>
+      <c r="F14" s="11">
+        <v>18</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="5" customHeight="1" spans="1:9">
-      <c r="A5" s="7">
-        <v>101</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7">
-        <v>101</v>
-      </c>
-      <c r="E5" s="7">
+    <row r="15" customHeight="1" spans="1:10">
+      <c r="A15" s="12">
+        <v>1051</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="12">
         <v>1</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="8">
-        <v>1004</v>
-      </c>
-      <c r="I5" s="8" t="s">
+      <c r="D15" s="12">
+        <v>1051</v>
+      </c>
+      <c r="E15" s="12">
+        <v>3</v>
+      </c>
+      <c r="F15" s="12">
         <v>20</v>
       </c>
+      <c r="G15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="12" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A6" s="9">
-        <v>201</v>
-      </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9">
-        <v>201</v>
-      </c>
-      <c r="E6" s="9">
-        <v>8</v>
-      </c>
-      <c r="F6" s="9">
-        <v>101</v>
-      </c>
-      <c r="G6" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="10">
-        <v>1846</v>
-      </c>
-      <c r="I6" s="9" t="s">
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A16" s="11">
+        <v>1061</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11">
+        <v>1061</v>
+      </c>
+      <c r="E16" s="11">
+        <v>3</v>
+      </c>
+      <c r="F16" s="11">
         <v>22</v>
       </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>45</v>
+      </c>
     </row>
-    <row r="7" s="4" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A7" s="11">
-        <v>301</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="11">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11">
-        <v>301</v>
-      </c>
-      <c r="E7" s="11">
-        <v>4</v>
-      </c>
-      <c r="F7" s="11">
-        <v>3</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A8" s="12">
-        <v>401</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="12">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12">
-        <v>401</v>
-      </c>
-      <c r="E8" s="12">
-        <v>4</v>
-      </c>
-      <c r="F8" s="12">
-        <v>5</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:9">
-      <c r="A9" s="11">
-        <v>501</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="11">
-        <v>1</v>
-      </c>
-      <c r="D9" s="11">
-        <v>501</v>
-      </c>
-      <c r="E9" s="11">
-        <v>4</v>
-      </c>
-      <c r="F9" s="11">
-        <v>8</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="10" s="3" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A10" s="12">
-        <v>1001</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="12">
-        <v>1</v>
-      </c>
-      <c r="D10" s="12">
-        <v>1001</v>
-      </c>
-      <c r="E10" s="12">
-        <v>4</v>
-      </c>
-      <c r="F10" s="12">
-        <v>10</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="12" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:9">
-      <c r="A11" s="11">
-        <v>1011</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="11">
-        <v>1</v>
-      </c>
-      <c r="D11" s="11">
-        <v>1011</v>
-      </c>
-      <c r="E11" s="11">
-        <v>4</v>
-      </c>
-      <c r="F11" s="11">
-        <v>12</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A12" s="12">
-        <v>1021</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="12">
-        <v>1021</v>
-      </c>
-      <c r="E12" s="12">
-        <v>4</v>
-      </c>
-      <c r="F12" s="12">
-        <v>14</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:9">
-      <c r="A13" s="11">
-        <v>1031</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="11">
-        <v>1</v>
-      </c>
-      <c r="D13" s="11">
-        <v>1031</v>
-      </c>
-      <c r="E13" s="11">
-        <v>4</v>
-      </c>
-      <c r="F13" s="11">
-        <v>16</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" s="3" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A14" s="12">
-        <v>1041</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="12">
-        <v>1</v>
-      </c>
-      <c r="D14" s="12">
-        <v>1041</v>
-      </c>
-      <c r="E14" s="12">
-        <v>4</v>
-      </c>
-      <c r="F14" s="12">
-        <v>18</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:9">
-      <c r="A15" s="11">
-        <v>1051</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C15" s="11">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11">
-        <v>1051</v>
-      </c>
-      <c r="E15" s="11">
-        <v>4</v>
-      </c>
-      <c r="F15" s="11">
-        <v>20</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:9">
-      <c r="A16" s="12">
-        <v>1061</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="12">
-        <v>1</v>
-      </c>
-      <c r="D16" s="12">
-        <v>1061</v>
-      </c>
-      <c r="E16" s="12">
-        <v>4</v>
-      </c>
-      <c r="F16" s="12">
-        <v>22</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="10:10">
-      <c r="J24" s="1"/>
+    <row r="24" customHeight="1" spans="11:11">
+      <c r="K24" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\A-work\config_SimMgmtVert1.0\游戏配置表\Manage\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Guide" sheetId="1" r:id="rId1"/>
@@ -163,7 +168,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
   <si>
     <t>序号</t>
   </si>
@@ -237,25 +242,34 @@
     <t>新手开场引导</t>
   </si>
   <si>
+    <t>经营大厅界面</t>
+  </si>
+  <si>
     <t>1841_1841_1842_1843_1844_1845_1846_1847_1848_1849_1850_1851_1852_1853</t>
   </si>
   <si>
     <t>解锁雇员&amp;雇员升级</t>
   </si>
   <si>
-    <t>经营大厅界面</t>
-  </si>
-  <si>
     <t>1861_1862_1863_1864_1865</t>
   </si>
   <si>
     <t>解锁联盟&amp;加入联盟</t>
   </si>
   <si>
-    <t>1201_1202_1203_1204_1205_1206_1207_1208_1209_1210_1211</t>
-  </si>
-  <si>
-    <t>试玩[超级明星]-默认解锁</t>
+    <t>1201_1202_1203_1204_1205</t>
+  </si>
+  <si>
+    <t>试玩[超级明星]-经营大厅</t>
+  </si>
+  <si>
+    <t>SLOT游戏</t>
+  </si>
+  <si>
+    <t>1206_1207_1208_1209_1210</t>
+  </si>
+  <si>
+    <t>试玩[超级明星]-SLOT游戏</t>
   </si>
   <si>
     <t>1301_1302_1303_1304_1305_1306_1307</t>
@@ -264,10 +278,16 @@
     <t>主线任务第1次引导</t>
   </si>
   <si>
-    <t>1401_1402_1403_1404_1405_1406_1407_1408_1409_1410_1411_1412_1413_1414_1415_1416_1417_1418_1419_1420_1421</t>
-  </si>
-  <si>
-    <t>研究院-SLOT升级词条-超级明星-解锁投注底数</t>
+    <t>1401_1402_1403_1404_1405_1406_1407_1408_1409_1410</t>
+  </si>
+  <si>
+    <t>研究院-SLOT升级词条-超级明星-经营大厅</t>
+  </si>
+  <si>
+    <t>1411_1412_1413_1414_1415_1416_1417_1418_1419</t>
+  </si>
+  <si>
+    <t>研究院-SLOT升级词条-超级明星-游戏中</t>
   </si>
   <si>
     <t>1501_1502_1503_1504_1505_1506_1507</t>
@@ -276,10 +296,16 @@
     <t>主线任务第2次引导</t>
   </si>
   <si>
-    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612_1613_1614_1615</t>
-  </si>
-  <si>
-    <t>研究院升级-解锁第2个游戏【麻将胡了】</t>
+    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610</t>
+  </si>
+  <si>
+    <t>研究院升级-解锁第2个游戏-经营大厅</t>
+  </si>
+  <si>
+    <t>1611_1612_1613_1614_1615</t>
+  </si>
+  <si>
+    <t>研究院升级-解锁第2个游戏-SLOT游戏</t>
   </si>
   <si>
     <t>1701_1702_1703_1704_1705_1706_1707_1708_1709</t>
@@ -301,6 +327,9 @@
   </si>
   <si>
     <t>赛季</t>
+  </si>
+  <si>
+    <t>斗仙牌</t>
   </si>
 </sst>
 </file>
@@ -313,7 +342,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -341,6 +370,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="0.6"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -826,137 +861,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -972,6 +1007,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -987,7 +1025,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1048,6 +1092,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="5" tint="0.4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1087,7 +1140,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16656050" y="1045210"/>
+          <a:off x="18011775" y="1045210"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1354,48 +1407,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="11.875" style="5" customWidth="1"/>
-    <col min="3" max="3" width="10.75" style="5" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="5" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="5" customWidth="1"/>
-    <col min="7" max="7" width="83.125" style="5" customWidth="1"/>
-    <col min="8" max="9" width="20.2833333333333" style="5" customWidth="1"/>
-    <col min="10" max="10" width="23.5" style="5" customWidth="1"/>
-    <col min="11" max="11" width="6.31666666666667" style="5" customWidth="1"/>
-    <col min="12" max="16384" width="15.625" style="5"/>
+    <col min="1" max="1" width="5.875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="13.6666666666667" style="6" customWidth="1"/>
+    <col min="3" max="3" width="10.75" style="6" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="6" customWidth="1"/>
+    <col min="7" max="7" width="83.125" style="6" customWidth="1"/>
+    <col min="8" max="9" width="20.2833333333333" style="6" customWidth="1"/>
+    <col min="10" max="10" width="39.5" style="6" customWidth="1"/>
+    <col min="11" max="11" width="6.31666666666667" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="15.625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1403,17 +1456,17 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1425,401 +1478,587 @@
       <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="7"/>
+      <c r="J2" s="8"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="7"/>
+      <c r="J3" s="8"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <v>101</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8">
+      <c r="C5" s="9"/>
+      <c r="D5" s="9">
         <v>101</v>
       </c>
-      <c r="E5" s="8">
-        <v>1</v>
-      </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9" t="s">
+      <c r="E5" s="9">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9"/>
+      <c r="G5" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="10">
         <v>1004</v>
       </c>
-      <c r="I5" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J5" s="9" t="s">
+      <c r="I5" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A6" s="8">
+      <c r="A6" s="9">
         <v>201</v>
       </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8">
+      <c r="B6" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="9">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9">
         <v>201</v>
       </c>
-      <c r="E6" s="8">
-        <v>8</v>
-      </c>
-      <c r="F6" s="8">
-        <v>101</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="E6" s="9">
+        <v>3</v>
+      </c>
+      <c r="F6" s="11">
+        <v>2</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1846</v>
+      </c>
+      <c r="I6" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A7" s="12">
+        <v>301</v>
+      </c>
+      <c r="B7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="9">
-        <v>1846</v>
-      </c>
-      <c r="I6" s="9" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A7" s="10">
+      <c r="C7" s="12">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12">
         <v>301</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1</v>
-      </c>
-      <c r="D7" s="10">
-        <v>301</v>
-      </c>
-      <c r="E7" s="10">
+      <c r="E7" s="12">
         <v>3</v>
       </c>
-      <c r="F7" s="10">
-        <v>3</v>
+      <c r="F7" s="13">
+        <v>4</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A8" s="11">
+      <c r="A8" s="14">
         <v>401</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="11">
-        <v>1</v>
-      </c>
-      <c r="D8" s="11">
+      <c r="B8" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="14">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
         <v>401</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="14">
         <v>3</v>
       </c>
-      <c r="F8" s="11">
-        <v>5</v>
+      <c r="F8" s="14">
+        <v>6</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="1:10">
-      <c r="A9" s="12">
-        <v>501</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="12">
-        <v>1</v>
-      </c>
-      <c r="D9" s="12">
-        <v>501</v>
-      </c>
-      <c r="E9" s="12">
+    <row r="9" s="5" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A9" s="14">
+        <v>402</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="14">
+        <v>2</v>
+      </c>
+      <c r="D9" s="14">
+        <v>402</v>
+      </c>
+      <c r="E9" s="14">
         <v>3</v>
       </c>
-      <c r="F9" s="12">
-        <v>8</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I9" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="12" t="s">
+      <c r="F9" s="13">
+        <v>9999</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A10" s="11">
-        <v>1001</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="11">
-        <v>1</v>
-      </c>
-      <c r="D10" s="11">
-        <v>1001</v>
-      </c>
-      <c r="E10" s="11">
+      <c r="H9" s="4"/>
+      <c r="I9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" s="5" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A10" s="14">
+        <v>403</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="14">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14">
+        <v>403</v>
+      </c>
+      <c r="E10" s="14">
         <v>3</v>
       </c>
-      <c r="F10" s="11">
-        <v>10</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>33</v>
+      <c r="F10" s="13">
+        <v>9999</v>
+      </c>
+      <c r="G10" s="4">
+        <v>1211</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J10" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:10">
+      <c r="A11" s="15">
+        <v>501</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="15">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15">
+        <v>501</v>
+      </c>
+      <c r="E11" s="15">
+        <v>3</v>
+      </c>
+      <c r="F11" s="15">
+        <v>9999</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:10">
-      <c r="A11" s="12">
-        <v>1011</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="12">
-        <v>1</v>
-      </c>
-      <c r="D11" s="12">
-        <v>1011</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="I11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A12" s="14">
+        <v>1001</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="14">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14">
+        <v>1001</v>
+      </c>
+      <c r="E12" s="14">
         <v>3</v>
       </c>
-      <c r="F11" s="12">
-        <v>12</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J11" s="12" t="s">
+      <c r="F12" s="14">
+        <v>8</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A12" s="11">
-        <v>1021</v>
-      </c>
-      <c r="B12" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="11">
-        <v>1</v>
-      </c>
-      <c r="D12" s="11">
-        <v>1021</v>
-      </c>
-      <c r="E12" s="11">
-        <v>3</v>
-      </c>
-      <c r="F12" s="11">
-        <v>14</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" s="5" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A13" s="14">
+        <v>1002</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="14">
+        <v>2</v>
+      </c>
+      <c r="D13" s="14">
+        <v>1002</v>
+      </c>
+      <c r="E13" s="14">
+        <v>3</v>
+      </c>
+      <c r="F13" s="13">
+        <v>9999</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:10">
-      <c r="A13" s="12">
-        <v>1031</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="12">
-        <v>1</v>
-      </c>
-      <c r="D13" s="12">
-        <v>1031</v>
-      </c>
-      <c r="E13" s="12">
+      <c r="H13" s="4"/>
+      <c r="I13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A14" s="14">
+        <v>1003</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1003</v>
+      </c>
+      <c r="E14" s="14">
         <v>3</v>
       </c>
-      <c r="F13" s="12">
-        <v>16</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A14" s="11">
-        <v>1041</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="11">
-        <v>1</v>
-      </c>
-      <c r="D14" s="11">
-        <v>1041</v>
-      </c>
-      <c r="E14" s="11">
-        <v>3</v>
-      </c>
-      <c r="F14" s="11">
-        <v>18</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>41</v>
+      <c r="F14" s="13">
+        <v>9999</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1420</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:10">
+      <c r="A15" s="15">
+        <v>1011</v>
+      </c>
+      <c r="B15" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1011</v>
+      </c>
+      <c r="E15" s="15">
+        <v>3</v>
+      </c>
+      <c r="F15" s="15">
+        <v>100</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A16" s="14">
+        <v>1021</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1021</v>
+      </c>
+      <c r="E16" s="14">
+        <v>3</v>
+      </c>
+      <c r="F16" s="14">
+        <v>10</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:10">
-      <c r="A15" s="12">
-        <v>1051</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="12">
-        <v>1</v>
-      </c>
-      <c r="D15" s="12">
-        <v>1051</v>
-      </c>
-      <c r="E15" s="12">
-        <v>3</v>
-      </c>
-      <c r="F15" s="12">
-        <v>20</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="I15" s="5" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="12" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A16" s="11">
-        <v>1061</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" s="11">
-        <v>1</v>
-      </c>
-      <c r="D16" s="11">
-        <v>1061</v>
-      </c>
-      <c r="E16" s="11">
-        <v>3</v>
-      </c>
-      <c r="F16" s="11">
-        <v>22</v>
-      </c>
-      <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" s="5" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A17" s="14">
+        <v>1022</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>1022</v>
+      </c>
+      <c r="E17" s="14">
+        <v>3</v>
+      </c>
+      <c r="F17" s="13">
+        <v>9999</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="24" customHeight="1" spans="11:11">
-      <c r="K24" s="1"/>
+    <row r="18" customHeight="1" spans="1:11">
+      <c r="A18" s="15">
+        <v>1031</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
+        <v>1031</v>
+      </c>
+      <c r="E18" s="15">
+        <v>3</v>
+      </c>
+      <c r="F18" s="15">
+        <v>16</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" s="4" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A19" s="14">
+        <v>1041</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="14">
+        <v>1</v>
+      </c>
+      <c r="D19" s="14">
+        <v>1041</v>
+      </c>
+      <c r="E19" s="14">
+        <v>3</v>
+      </c>
+      <c r="F19" s="14">
+        <v>18</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="14" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:11">
+      <c r="A20" s="15">
+        <v>1051</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
+        <v>1051</v>
+      </c>
+      <c r="E20" s="15">
+        <v>3</v>
+      </c>
+      <c r="F20" s="15">
+        <v>20</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="I20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" s="4" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A21" s="14">
+        <v>1061</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="14">
+        <v>1</v>
+      </c>
+      <c r="D21" s="14">
+        <v>1061</v>
+      </c>
+      <c r="E21" s="14">
+        <v>3</v>
+      </c>
+      <c r="F21" s="13">
+        <v>9999</v>
+      </c>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="22" s="6" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A22" s="15">
+        <v>1071</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
+        <v>1071</v>
+      </c>
+      <c r="E22" s="15">
+        <v>3</v>
+      </c>
+      <c r="F22" s="15">
+        <v>9999</v>
+      </c>
+      <c r="I22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:11">
+      <c r="K29" s="1"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:A21 A23:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -991,7 +991,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1025,16 +1025,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1115,15 +1109,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>120015</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>29210</xdr:rowOff>
+      <xdr:colOff>29845</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>230505</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>784225</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>247650</xdr:rowOff>
+      <xdr:colOff>694055</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>194945</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1140,7 +1134,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18011775" y="1045210"/>
+          <a:off x="17921605" y="2770505"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1561,10 +1555,10 @@
         <v>201</v>
       </c>
       <c r="E6" s="9">
-        <v>3</v>
-      </c>
-      <c r="F6" s="11">
-        <v>2</v>
+        <v>8</v>
+      </c>
+      <c r="F6" s="9">
+        <v>101</v>
       </c>
       <c r="G6" s="10" t="s">
         <v>25</v>
@@ -1580,52 +1574,52 @@
       </c>
     </row>
     <row r="7" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A7" s="12">
+      <c r="A7" s="9">
         <v>301</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="12">
-        <v>1</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="C7" s="9">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9">
         <v>301</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="9">
+        <v>8</v>
+      </c>
+      <c r="F7" s="9">
+        <v>201</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A8" s="11">
+        <v>401</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11">
+        <v>401</v>
+      </c>
+      <c r="E8" s="11">
         <v>3</v>
       </c>
-      <c r="F7" s="13">
-        <v>4</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A8" s="14">
-        <v>401</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="14">
-        <v>1</v>
-      </c>
-      <c r="D8" s="14">
-        <v>401</v>
-      </c>
-      <c r="E8" s="14">
-        <v>3</v>
-      </c>
-      <c r="F8" s="14">
+      <c r="F8" s="11">
         <v>6</v>
       </c>
       <c r="G8" s="4" t="s">
@@ -1640,22 +1634,22 @@
       </c>
     </row>
     <row r="9" s="5" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A9" s="14">
+      <c r="A9" s="11">
         <v>402</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C9" s="11">
         <v>2</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="11">
         <v>402</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="11">
         <v>3</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="12">
         <v>9999</v>
       </c>
       <c r="G9" s="4" t="s">
@@ -1670,22 +1664,22 @@
       </c>
     </row>
     <row r="10" s="5" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A10" s="14">
+      <c r="A10" s="11">
         <v>403</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="14">
-        <v>1</v>
-      </c>
-      <c r="D10" s="14">
+      <c r="C10" s="11">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11">
         <v>403</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="11">
         <v>3</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="12">
         <v>9999</v>
       </c>
       <c r="G10" s="4">
@@ -1700,22 +1694,22 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:10">
-      <c r="A11" s="15">
+      <c r="A11" s="13">
         <v>501</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="15">
-        <v>1</v>
-      </c>
-      <c r="D11" s="15">
+      <c r="C11" s="13">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13">
         <v>501</v>
       </c>
-      <c r="E11" s="15">
+      <c r="E11" s="13">
         <v>3</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="13">
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -1724,27 +1718,27 @@
       <c r="I11" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="13" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A12" s="14">
+      <c r="A12" s="11">
         <v>1001</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="14">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14">
+      <c r="C12" s="11">
+        <v>1</v>
+      </c>
+      <c r="D12" s="11">
         <v>1001</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E12" s="11">
         <v>3</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="11">
         <v>8</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -1754,27 +1748,27 @@
       <c r="I12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="J12" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" s="5" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A13" s="14">
+      <c r="A13" s="11">
         <v>1002</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="11">
         <v>2</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="11">
         <v>1002</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="11">
         <v>3</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="12">
         <v>9999</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -1784,27 +1778,27 @@
       <c r="I13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J13" s="14" t="s">
+      <c r="J13" s="11" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" s="5" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A14" s="14">
+      <c r="A14" s="11">
         <v>1003</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="14">
+      <c r="C14" s="11">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11">
         <v>1003</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="11">
         <v>3</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="12">
         <v>9999</v>
       </c>
       <c r="G14" s="4">
@@ -1814,27 +1808,27 @@
       <c r="I14" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="11" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:10">
-      <c r="A15" s="15">
+      <c r="A15" s="13">
         <v>1011</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
+      <c r="C15" s="13">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13">
         <v>1011</v>
       </c>
-      <c r="E15" s="15">
+      <c r="E15" s="13">
         <v>3</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="13">
         <v>100</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -1843,27 +1837,27 @@
       <c r="I15" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="13" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A16" s="14">
+      <c r="A16" s="11">
         <v>1021</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
+      <c r="C16" s="11">
+        <v>1</v>
+      </c>
+      <c r="D16" s="11">
         <v>1021</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="11">
         <v>3</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="11">
         <v>10</v>
       </c>
       <c r="G16" s="4" t="s">
@@ -1873,27 +1867,27 @@
       <c r="I16" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="11" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="17" s="5" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A17" s="14">
+      <c r="A17" s="11">
         <v>1022</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B17" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="11">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="11">
         <v>1022</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="11">
         <v>3</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="12">
         <v>9999</v>
       </c>
       <c r="G17" s="4" t="s">
@@ -1903,27 +1897,27 @@
       <c r="I17" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="11" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="15">
+      <c r="A18" s="13">
         <v>1031</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
+      <c r="C18" s="13">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13">
         <v>1031</v>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="13">
         <v>3</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="13">
         <v>16</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -1932,27 +1926,27 @@
       <c r="I18" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J18" s="15" t="s">
+      <c r="J18" s="13" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A19" s="14">
+      <c r="A19" s="11">
         <v>1041</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="14">
-        <v>1</v>
-      </c>
-      <c r="D19" s="14">
+      <c r="C19" s="11">
+        <v>1</v>
+      </c>
+      <c r="D19" s="11">
         <v>1041</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E19" s="11">
         <v>3</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="11">
         <v>18</v>
       </c>
       <c r="G19" s="4" t="s">
@@ -1962,27 +1956,27 @@
       <c r="I19" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J19" s="14" t="s">
+      <c r="J19" s="11" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:11">
-      <c r="A20" s="15">
+      <c r="A20" s="13">
         <v>1051</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="B20" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="13">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13">
         <v>1051</v>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="13">
         <v>3</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="13">
         <v>20</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -1991,27 +1985,27 @@
       <c r="I20" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="13" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A21" s="14">
+      <c r="A21" s="11">
         <v>1061</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="14">
-        <v>1</v>
-      </c>
-      <c r="D21" s="14">
+      <c r="C21" s="11">
+        <v>1</v>
+      </c>
+      <c r="D21" s="11">
         <v>1061</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="11">
         <v>3</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="12">
         <v>9999</v>
       </c>
       <c r="G21" s="4"/>
@@ -2024,22 +2018,22 @@
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A22" s="15">
+      <c r="A22" s="13">
         <v>1071</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="13">
+        <v>1</v>
+      </c>
+      <c r="D22" s="13">
         <v>1071</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="13">
         <v>3</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="13">
         <v>9999</v>
       </c>
       <c r="I22" s="6" t="b">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -991,7 +991,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1024,6 +1024,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1587,10 +1590,10 @@
         <v>301</v>
       </c>
       <c r="E7" s="9">
-        <v>8</v>
-      </c>
-      <c r="F7" s="9">
-        <v>201</v>
+        <v>3</v>
+      </c>
+      <c r="F7" s="11">
+        <v>3</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>27</v>
@@ -1604,22 +1607,22 @@
       </c>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A8" s="11">
+      <c r="A8" s="12">
         <v>401</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="11">
-        <v>1</v>
-      </c>
-      <c r="D8" s="11">
+      <c r="C8" s="12">
+        <v>1</v>
+      </c>
+      <c r="D8" s="12">
         <v>401</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="12">
         <v>3</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="12">
         <v>6</v>
       </c>
       <c r="G8" s="4" t="s">
@@ -1634,22 +1637,22 @@
       </c>
     </row>
     <row r="9" s="5" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A9" s="11">
+      <c r="A9" s="12">
         <v>402</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <v>2</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <v>402</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="12">
         <v>3</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <v>9999</v>
       </c>
       <c r="G9" s="4" t="s">
@@ -1664,22 +1667,22 @@
       </c>
     </row>
     <row r="10" s="5" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A10" s="11">
+      <c r="A10" s="12">
         <v>403</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="11">
-        <v>1</v>
-      </c>
-      <c r="D10" s="11">
+      <c r="C10" s="12">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12">
         <v>403</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="12">
         <v>3</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <v>9999</v>
       </c>
       <c r="G10" s="4">
@@ -1694,22 +1697,22 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:10">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>501</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
-      <c r="D11" s="13">
+      <c r="C11" s="14">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14">
         <v>501</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="14">
         <v>3</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <v>9999</v>
       </c>
       <c r="G11" s="6" t="s">
@@ -1718,27 +1721,27 @@
       <c r="I11" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A12" s="11">
+      <c r="A12" s="12">
         <v>1001</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="11">
-        <v>1</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="C12" s="12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="12">
         <v>1001</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="12">
         <v>3</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="12">
         <v>8</v>
       </c>
       <c r="G12" s="4" t="s">
@@ -1748,27 +1751,27 @@
       <c r="I12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="13" s="5" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A13" s="11">
+      <c r="A13" s="12">
         <v>1002</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="12">
         <v>2</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="12">
         <v>1002</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="12">
         <v>3</v>
       </c>
-      <c r="F13" s="12">
+      <c r="F13" s="13">
         <v>9999</v>
       </c>
       <c r="G13" s="4" t="s">
@@ -1778,27 +1781,27 @@
       <c r="I13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" s="5" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A14" s="11">
+      <c r="A14" s="12">
         <v>1003</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="11">
-        <v>1</v>
-      </c>
-      <c r="D14" s="11">
+      <c r="C14" s="12">
+        <v>1</v>
+      </c>
+      <c r="D14" s="12">
         <v>1003</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="12">
         <v>3</v>
       </c>
-      <c r="F14" s="12">
+      <c r="F14" s="13">
         <v>9999</v>
       </c>
       <c r="G14" s="4">
@@ -1808,27 +1811,27 @@
       <c r="I14" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="11" t="s">
+      <c r="J14" s="12" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:10">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>1011</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="13">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
         <v>1011</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="14">
         <v>3</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <v>100</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -1837,27 +1840,27 @@
       <c r="I15" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="14" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" s="4" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A16" s="11">
+      <c r="A16" s="12">
         <v>1021</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="11">
-        <v>1</v>
-      </c>
-      <c r="D16" s="11">
+      <c r="C16" s="12">
+        <v>1</v>
+      </c>
+      <c r="D16" s="12">
         <v>1021</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16" s="12">
         <v>3</v>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="12">
         <v>10</v>
       </c>
       <c r="G16" s="4" t="s">
@@ -1867,27 +1870,27 @@
       <c r="I16" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="11" t="s">
+      <c r="J16" s="12" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="17" s="5" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A17" s="11">
+      <c r="A17" s="12">
         <v>1022</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="12">
         <v>2</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="12">
         <v>1022</v>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="12">
         <v>3</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="13">
         <v>9999</v>
       </c>
       <c r="G17" s="4" t="s">
@@ -1897,27 +1900,27 @@
       <c r="I17" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J17" s="11" t="s">
+      <c r="J17" s="12" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="13">
+      <c r="A18" s="14">
         <v>1031</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="13">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13">
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>1031</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="14">
         <v>3</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <v>16</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -1926,27 +1929,27 @@
       <c r="I18" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J18" s="13" t="s">
+      <c r="J18" s="14" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="19" s="4" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A19" s="11">
+      <c r="A19" s="12">
         <v>1041</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="11">
-        <v>1</v>
-      </c>
-      <c r="D19" s="11">
+      <c r="C19" s="12">
+        <v>1</v>
+      </c>
+      <c r="D19" s="12">
         <v>1041</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="12">
         <v>3</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="12">
         <v>18</v>
       </c>
       <c r="G19" s="4" t="s">
@@ -1956,27 +1959,27 @@
       <c r="I19" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="J19" s="11" t="s">
+      <c r="J19" s="12" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:11">
-      <c r="A20" s="13">
+      <c r="A20" s="14">
         <v>1051</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="13">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13">
+      <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
         <v>1051</v>
       </c>
-      <c r="E20" s="13">
+      <c r="E20" s="14">
         <v>3</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <v>20</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -1985,27 +1988,27 @@
       <c r="I20" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="J20" s="13" t="s">
+      <c r="J20" s="14" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="21" s="4" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A21" s="11">
+      <c r="A21" s="12">
         <v>1061</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="11">
-        <v>1</v>
-      </c>
-      <c r="D21" s="11">
+      <c r="C21" s="12">
+        <v>1</v>
+      </c>
+      <c r="D21" s="12">
         <v>1061</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="12">
         <v>3</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F21" s="13">
         <v>9999</v>
       </c>
       <c r="G21" s="4"/>
@@ -2018,22 +2021,22 @@
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A22" s="13">
+      <c r="A22" s="14">
         <v>1071</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="13">
-        <v>1</v>
-      </c>
-      <c r="D22" s="13">
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
         <v>1071</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="14">
         <v>3</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <v>9999</v>
       </c>
       <c r="I22" s="6" t="b">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -524,12 +524,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1593,7 +1593,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="11">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>27</v>
@@ -1950,7 +1950,7 @@
         <v>3</v>
       </c>
       <c r="F19" s="12">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>48</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -524,12 +524,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1404,7 +1404,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="6" customWidth="1"/>
@@ -1420,7 +1420,7 @@
     <col min="12" max="16384" width="15.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="J2" s="8"/>
     </row>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:10">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
       <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
@@ -1508,7 +1508,7 @@
       </c>
       <c r="J3" s="8"/>
     </row>
-    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:10">
+    <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
       <c r="A4" s="7"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1516,7 +1516,7 @@
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" s="3" customFormat="1" customHeight="1" spans="1:10">
+    <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A5" s="9">
         <v>101</v>
       </c>
@@ -1543,8 +1543,12 @@
       <c r="J5" s="10" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="L5" s="3" t="str">
+        <f>SUBSTITUTE(G5,"_",",")</f>
+        <v>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014</v>
+      </c>
+    </row>
+    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A6" s="9">
         <v>201</v>
       </c>
@@ -1576,7 +1580,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:10">
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A7" s="9">
         <v>301</v>
       </c>
@@ -1606,7 +1610,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A8" s="12">
         <v>401</v>
       </c>
@@ -1636,7 +1640,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" s="5" customFormat="1" customHeight="1" spans="1:10">
+    <row r="9" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A9" s="12">
         <v>402</v>
       </c>
@@ -1666,7 +1670,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" s="5" customFormat="1" customHeight="1" spans="1:10">
+    <row r="10" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A10" s="12">
         <v>403</v>
       </c>
@@ -1696,7 +1700,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:10">
+    <row r="11" customHeight="1" spans="1:12">
       <c r="A11" s="14">
         <v>501</v>
       </c>
@@ -1725,7 +1729,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A12" s="12">
         <v>1001</v>
       </c>
@@ -1755,7 +1759,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" s="5" customFormat="1" customHeight="1" spans="1:10">
+    <row r="13" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A13" s="12">
         <v>1002</v>
       </c>
@@ -1785,7 +1789,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:10">
+    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:12">
       <c r="A14" s="12">
         <v>1003</v>
       </c>
@@ -1815,7 +1819,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="1:10">
+    <row r="15" customHeight="1" spans="1:12">
       <c r="A15" s="14">
         <v>1011</v>
       </c>
@@ -1844,7 +1848,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:10">
+    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A16" s="12">
         <v>1021</v>
       </c>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -342,7 +342,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -365,6 +365,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B0F0"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.35"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -861,137 +867,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1013,6 +1019,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1025,10 +1034,10 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1407,45 +1416,45 @@
   <dimension ref="A1:L29"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="13.6666666666667" style="6" customWidth="1"/>
-    <col min="3" max="3" width="10.75" style="6" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="6" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="6" customWidth="1"/>
-    <col min="7" max="7" width="83.125" style="6" customWidth="1"/>
-    <col min="8" max="9" width="20.2833333333333" style="6" customWidth="1"/>
-    <col min="10" max="10" width="39.5" style="6" customWidth="1"/>
-    <col min="11" max="11" width="6.31666666666667" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="15.625" style="6"/>
+    <col min="1" max="1" width="5.875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="13.6666666666667" style="7" customWidth="1"/>
+    <col min="3" max="3" width="10.75" style="7" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="7" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="7" customWidth="1"/>
+    <col min="7" max="7" width="83.125" style="7" customWidth="1"/>
+    <col min="8" max="9" width="20.2833333333333" style="7" customWidth="1"/>
+    <col min="10" max="10" width="39.5" style="7" customWidth="1"/>
+    <col min="11" max="11" width="6.31666666666667" style="7" customWidth="1"/>
+    <col min="12" max="16384" width="15.625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1453,17 +1462,17 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -1475,138 +1484,138 @@
       <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="8"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>17</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="8"/>
+      <c r="J3" s="9"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="9">
+      <c r="A5" s="10">
         <v>101</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B5" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9">
+      <c r="C5" s="10"/>
+      <c r="D5" s="10">
         <v>101</v>
       </c>
-      <c r="E5" s="9">
-        <v>1</v>
-      </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="10" t="s">
+      <c r="E5" s="10">
+        <v>1</v>
+      </c>
+      <c r="F5" s="10"/>
+      <c r="G5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="11">
         <v>1004</v>
       </c>
-      <c r="I5" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" s="10" t="s">
+      <c r="I5" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>23</v>
       </c>
       <c r="L5" s="3" t="str">
-        <f>SUBSTITUTE(G5,"_",",")</f>
-        <v>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013,1014</v>
+        <f>SUBSTITUTE(G16,"_",",")</f>
+        <v>1601,1602,1603,1604,1605,1606,1607,1608,1609,1610</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="9">
+      <c r="A6" s="10">
         <v>201</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="9">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9">
+      <c r="C6" s="10">
+        <v>1</v>
+      </c>
+      <c r="D6" s="10">
         <v>201</v>
       </c>
-      <c r="E6" s="9">
-        <v>8</v>
-      </c>
-      <c r="F6" s="9">
-        <v>101</v>
-      </c>
-      <c r="G6" s="10" t="s">
+      <c r="E6" s="10">
+        <v>3</v>
+      </c>
+      <c r="F6" s="10">
+        <v>32</v>
+      </c>
+      <c r="G6" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="11">
         <v>1846</v>
       </c>
-      <c r="I6" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="9" t="s">
+      <c r="I6" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="9">
+      <c r="A7" s="10">
         <v>301</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="9">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9">
+      <c r="C7" s="10">
+        <v>1</v>
+      </c>
+      <c r="D7" s="10">
         <v>301</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="10">
         <v>3</v>
       </c>
-      <c r="F7" s="11">
-        <v>4</v>
-      </c>
-      <c r="G7" s="10" t="s">
+      <c r="F7" s="10">
+        <v>34</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9" t="s">
+      <c r="H7" s="11"/>
+      <c r="I7" s="11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="10" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1626,8 +1635,8 @@
       <c r="E8" s="12">
         <v>3</v>
       </c>
-      <c r="F8" s="12">
-        <v>6</v>
+      <c r="F8" s="13">
+        <v>36</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>29</v>
@@ -1657,7 +1666,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="13">
-        <v>9999</v>
+        <v>38</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>32</v>
@@ -1687,7 +1696,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="13">
-        <v>9999</v>
+        <v>40</v>
       </c>
       <c r="G10" s="4">
         <v>1211</v>
@@ -1716,13 +1725,13 @@
       <c r="E11" s="14">
         <v>3</v>
       </c>
-      <c r="F11" s="14">
-        <v>9999</v>
-      </c>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="13">
+        <v>42</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="6" t="b">
+      <c r="I11" s="7" t="b">
         <v>1</v>
       </c>
       <c r="J11" s="14" t="s">
@@ -1745,8 +1754,8 @@
       <c r="E12" s="12">
         <v>3</v>
       </c>
-      <c r="F12" s="12">
-        <v>8</v>
+      <c r="F12" s="13">
+        <v>44</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>36</v>
@@ -1776,7 +1785,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="13">
-        <v>9999</v>
+        <v>46</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>38</v>
@@ -1806,7 +1815,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="13">
-        <v>9999</v>
+        <v>48</v>
       </c>
       <c r="G14" s="4">
         <v>1420</v>
@@ -1835,13 +1844,13 @@
       <c r="E15" s="14">
         <v>3</v>
       </c>
-      <c r="F15" s="14">
-        <v>100</v>
-      </c>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="13">
+        <v>50</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="I15" s="6" t="b">
+      <c r="I15" s="7" t="b">
         <v>1</v>
       </c>
       <c r="J15" s="14" t="s">
@@ -1864,8 +1873,8 @@
       <c r="E16" s="12">
         <v>3</v>
       </c>
-      <c r="F16" s="12">
-        <v>10</v>
+      <c r="F16" s="13">
+        <v>52</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>42</v>
@@ -1895,7 +1904,7 @@
         <v>3</v>
       </c>
       <c r="F17" s="13">
-        <v>9999</v>
+        <v>54</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>44</v>
@@ -1924,13 +1933,13 @@
       <c r="E18" s="14">
         <v>3</v>
       </c>
-      <c r="F18" s="14">
-        <v>16</v>
-      </c>
-      <c r="G18" s="6" t="s">
+      <c r="F18" s="13">
+        <v>56</v>
+      </c>
+      <c r="G18" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I18" s="6" t="b">
+      <c r="I18" s="7" t="b">
         <v>1</v>
       </c>
       <c r="J18" s="14" t="s">
@@ -1953,8 +1962,8 @@
       <c r="E19" s="12">
         <v>3</v>
       </c>
-      <c r="F19" s="12">
-        <v>3</v>
+      <c r="F19" s="13">
+        <v>58</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>48</v>
@@ -1983,64 +1992,64 @@
       <c r="E20" s="14">
         <v>3</v>
       </c>
-      <c r="F20" s="14">
-        <v>20</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="13">
+        <v>60</v>
+      </c>
+      <c r="G20" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I20" s="6" t="b">
+      <c r="I20" s="7" t="b">
         <v>1</v>
       </c>
       <c r="J20" s="14" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="21" s="4" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A21" s="12">
+    <row r="21" s="6" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A21" s="15">
         <v>1061</v>
       </c>
-      <c r="B21" s="12" t="s">
+      <c r="B21" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="12">
-        <v>1</v>
-      </c>
-      <c r="D21" s="12">
+      <c r="C21" s="15">
+        <v>1</v>
+      </c>
+      <c r="D21" s="15">
         <v>1061</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E21" s="15">
         <v>3</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="15">
         <v>9999</v>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" s="4" t="s">
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="6" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A22" s="14">
+      <c r="A22" s="15">
         <v>1071</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="15">
+        <v>1</v>
+      </c>
+      <c r="D22" s="15">
         <v>1071</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E22" s="15">
         <v>3</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="15">
         <v>9999</v>
       </c>
       <c r="I22" s="6" t="b">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -342,7 +342,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -382,6 +382,12 @@
     <font>
       <sz val="11"/>
       <color theme="9" tint="0.6"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -867,137 +873,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1038,6 +1044,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1662,11 +1671,11 @@
       <c r="D9" s="12">
         <v>402</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="14">
         <v>3</v>
       </c>
-      <c r="F9" s="13">
-        <v>38</v>
+      <c r="F9" s="14">
+        <v>9999</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>32</v>
@@ -1710,19 +1719,19 @@
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="14">
+      <c r="A11" s="15">
         <v>501</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="14">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14">
+      <c r="C11" s="15">
+        <v>1</v>
+      </c>
+      <c r="D11" s="15">
         <v>501</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E11" s="15">
         <v>3</v>
       </c>
       <c r="F11" s="13">
@@ -1734,7 +1743,7 @@
       <c r="I11" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="J11" s="15" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1781,11 +1790,11 @@
       <c r="D13" s="12">
         <v>1002</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E13" s="14">
         <v>3</v>
       </c>
-      <c r="F13" s="13">
-        <v>46</v>
+      <c r="F13" s="14">
+        <v>9999</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>38</v>
@@ -1829,19 +1838,19 @@
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="14">
+      <c r="A15" s="15">
         <v>1011</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
         <v>1011</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="15">
         <v>3</v>
       </c>
       <c r="F15" s="13">
@@ -1853,7 +1862,7 @@
       <c r="I15" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="14" t="s">
+      <c r="J15" s="15" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1900,11 +1909,11 @@
       <c r="D17" s="12">
         <v>1022</v>
       </c>
-      <c r="E17" s="12">
+      <c r="E17" s="14">
         <v>3</v>
       </c>
-      <c r="F17" s="13">
-        <v>54</v>
+      <c r="F17" s="14">
+        <v>9999</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>44</v>
@@ -1918,19 +1927,19 @@
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="14">
+      <c r="A18" s="15">
         <v>1031</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
+      <c r="C18" s="15">
+        <v>1</v>
+      </c>
+      <c r="D18" s="15">
         <v>1031</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E18" s="15">
         <v>3</v>
       </c>
       <c r="F18" s="13">
@@ -1942,7 +1951,7 @@
       <c r="I18" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="J18" s="15" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1977,19 +1986,19 @@
       </c>
     </row>
     <row r="20" customHeight="1" spans="1:11">
-      <c r="A20" s="14">
+      <c r="A20" s="15">
         <v>1051</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
+      <c r="C20" s="15">
+        <v>1</v>
+      </c>
+      <c r="D20" s="15">
         <v>1051</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E20" s="15">
         <v>3</v>
       </c>
       <c r="F20" s="13">
@@ -2001,27 +2010,27 @@
       <c r="I20" s="7" t="b">
         <v>1</v>
       </c>
-      <c r="J20" s="14" t="s">
+      <c r="J20" s="15" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="21" s="6" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A21" s="15">
+      <c r="A21" s="16">
         <v>1061</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="15">
-        <v>1</v>
-      </c>
-      <c r="D21" s="15">
+      <c r="C21" s="16">
+        <v>1</v>
+      </c>
+      <c r="D21" s="16">
         <v>1061</v>
       </c>
-      <c r="E21" s="15">
+      <c r="E21" s="16">
         <v>3</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="16">
         <v>9999</v>
       </c>
       <c r="G21" s="6"/>
@@ -2034,22 +2043,22 @@
       </c>
     </row>
     <row r="22" s="6" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A22" s="15">
+      <c r="A22" s="16">
         <v>1071</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
-      </c>
-      <c r="D22" s="15">
+      <c r="C22" s="16">
+        <v>1</v>
+      </c>
+      <c r="D22" s="16">
         <v>1071</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E22" s="16">
         <v>3</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="16">
         <v>9999</v>
       </c>
       <c r="I22" s="6" t="b">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -109,7 +109,8 @@
 5. 道具不足触发(道具不足)
 6. 获得指定道具ID触发
 7. 功能解锁触发(回到经营大厅 填写功能ID，GameFunction.xlsx 表中ID )
-8.  引导组触发(填写的引导组完成后触发) </t>
+8.  引导组触发(填写的引导组完成后触发) 
+9. 功能界面首次打开触发</t>
         </r>
       </text>
     </comment>
@@ -168,7 +169,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>序号</t>
   </si>
@@ -233,103 +234,70 @@
     <t>isOpen</t>
   </si>
   <si>
-    <t>创建新号</t>
-  </si>
-  <si>
-    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013_1014</t>
-  </si>
-  <si>
-    <t>新手开场引导</t>
-  </si>
-  <si>
-    <t>经营大厅界面</t>
-  </si>
-  <si>
-    <t>1841_1841_1842_1843_1844_1845_1846_1847_1848_1849_1850_1851_1852_1853</t>
-  </si>
-  <si>
-    <t>解锁雇员&amp;雇员升级</t>
-  </si>
-  <si>
-    <t>1861_1862_1863_1864_1865</t>
-  </si>
-  <si>
-    <t>解锁联盟&amp;加入联盟</t>
-  </si>
-  <si>
-    <t>1201_1202_1203_1204_1205</t>
-  </si>
-  <si>
-    <t>试玩[超级明星]-经营大厅</t>
-  </si>
-  <si>
-    <t>SLOT游戏</t>
-  </si>
-  <si>
-    <t>1206_1207_1208_1209_1210</t>
-  </si>
-  <si>
-    <t>试玩[超级明星]-SLOT游戏</t>
-  </si>
-  <si>
-    <t>1301_1302_1303_1304_1305_1306_1307</t>
-  </si>
-  <si>
-    <t>主线任务第1次引导</t>
-  </si>
-  <si>
-    <t>1401_1402_1403_1404_1405_1406_1407_1408_1409_1410</t>
-  </si>
-  <si>
-    <t>研究院-SLOT升级词条-超级明星-经营大厅</t>
-  </si>
-  <si>
-    <t>1411_1412_1413_1414_1415_1416_1417_1418_1419</t>
-  </si>
-  <si>
-    <t>研究院-SLOT升级词条-超级明星-游戏中</t>
-  </si>
-  <si>
-    <t>1501_1502_1503_1504_1505_1506_1507</t>
-  </si>
-  <si>
-    <t>主线任务第2次引导</t>
-  </si>
-  <si>
-    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610</t>
-  </si>
-  <si>
-    <t>研究院升级-解锁第2个游戏-经营大厅</t>
-  </si>
-  <si>
-    <t>1611_1612_1613_1614_1615</t>
-  </si>
-  <si>
-    <t>研究院升级-解锁第2个游戏-SLOT游戏</t>
-  </si>
-  <si>
-    <t>1701_1702_1703_1704_1705_1706_1707_1708_1709</t>
-  </si>
-  <si>
-    <t>解锁捕鱼机台建筑-1110</t>
-  </si>
-  <si>
-    <t>1801_1802_1803_1804_1805_1806_1807_1808_1809_1810</t>
-  </si>
-  <si>
-    <t>解锁游客&amp;游客升星</t>
-  </si>
-  <si>
-    <t>1821_1822_1823_1824_1825_1826_1827</t>
-  </si>
-  <si>
-    <t>主线任务第3次引导</t>
-  </si>
-  <si>
-    <t>赛季</t>
-  </si>
-  <si>
-    <t>斗仙牌</t>
+    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012</t>
+  </si>
+  <si>
+    <t>初入游戏-创建新号到经营大厅</t>
+  </si>
+  <si>
+    <t>1201_1202_1203</t>
+  </si>
+  <si>
+    <t>建筑-愤怒的小鸟-升级1次</t>
+  </si>
+  <si>
+    <t>1301_1302_1303_1304_1305_1306</t>
+  </si>
+  <si>
+    <t>建筑-愤怒的小鸟-SLOT</t>
+  </si>
+  <si>
+    <t>1401_1402_1403_1404_1405_1406</t>
+  </si>
+  <si>
+    <t>建筑-愤怒的小鸟-升到2级</t>
+  </si>
+  <si>
+    <t>1501_1502_1503_1504</t>
+  </si>
+  <si>
+    <t>建筑-愤怒的小鸟-SLOT2</t>
+  </si>
+  <si>
+    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612</t>
+  </si>
+  <si>
+    <t>雇员-抽卡-升级-升星</t>
+  </si>
+  <si>
+    <t>1701_1702_1703_1704_1705_1706_1707_1708_1709_1710_1711_1712</t>
+  </si>
+  <si>
+    <t>游客-抽卡-升星</t>
+  </si>
+  <si>
+    <t>1801_1802_1803_1804_1805_1806_1807</t>
+  </si>
+  <si>
+    <t>建筑-象财神-升级</t>
+  </si>
+  <si>
+    <t>1901_1902_1903_1904</t>
+  </si>
+  <si>
+    <t>赛季-界面</t>
+  </si>
+  <si>
+    <t>2001_2002_2003_2004_2005_2006_2007_2008</t>
+  </si>
+  <si>
+    <t>赛季-斗仙牌</t>
+  </si>
+  <si>
+    <t>2101_2102_2103</t>
+  </si>
+  <si>
+    <t>联盟</t>
   </si>
 </sst>
 </file>
@@ -342,7 +310,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,36 +326,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="9" tint="0.6"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -556,7 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
+        <fgColor theme="7" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -873,137 +811,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1016,43 +954,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1155,7 +1078,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17921605" y="2770505"/>
+          <a:off x="18213070" y="2770505"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1422,48 +1345,48 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L29"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="13.6666666666667" style="7" customWidth="1"/>
-    <col min="3" max="3" width="10.75" style="7" customWidth="1"/>
-    <col min="4" max="4" width="13.875" style="7" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="7" customWidth="1"/>
-    <col min="7" max="7" width="83.125" style="7" customWidth="1"/>
-    <col min="8" max="9" width="20.2833333333333" style="7" customWidth="1"/>
-    <col min="10" max="10" width="39.5" style="7" customWidth="1"/>
-    <col min="11" max="11" width="6.31666666666667" style="7" customWidth="1"/>
-    <col min="12" max="16384" width="15.625" style="7"/>
+    <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="17.4916666666667" style="3" customWidth="1"/>
+    <col min="3" max="3" width="10.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="13.875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="11.875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="3" customWidth="1"/>
+    <col min="7" max="7" width="83.125" style="3" customWidth="1"/>
+    <col min="8" max="9" width="20.2833333333333" style="3" customWidth="1"/>
+    <col min="10" max="10" width="39.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="6.31666666666667" style="3" customWidth="1"/>
+    <col min="12" max="16384" width="15.625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1471,611 +1394,380 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="7" t="s">
         <v>12</v>
       </c>
       <c r="J2" s="9"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="5"/>
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="9"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
+      <c r="A4" s="10"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
     </row>
     <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="10">
+      <c r="A5" s="11">
         <v>101</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="C5" s="11"/>
+      <c r="D5" s="11">
+        <v>101</v>
+      </c>
+      <c r="E5" s="11">
+        <v>1</v>
+      </c>
+      <c r="F5" s="11"/>
+      <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10">
-        <v>101</v>
-      </c>
-      <c r="E5" s="10">
-        <v>1</v>
-      </c>
-      <c r="F5" s="10"/>
-      <c r="G5" s="11" t="s">
+      <c r="H5" s="3">
+        <v>1004</v>
+      </c>
+      <c r="I5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="11">
-        <v>1004</v>
-      </c>
-      <c r="I5" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" s="11" t="s">
-        <v>23</v>
-      </c>
       <c r="L5" s="3" t="str">
-        <f>SUBSTITUTE(G16,"_",",")</f>
-        <v>1601,1602,1603,1604,1605,1606,1607,1608,1609,1610</v>
+        <f>SUBSTITUTE(G5,"_",",")</f>
+        <v>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="10">
+      <c r="A6" s="11">
         <v>201</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="C6" s="11">
+        <v>1</v>
+      </c>
+      <c r="D6" s="11">
+        <v>201</v>
+      </c>
+      <c r="E6" s="11">
+        <v>3</v>
+      </c>
+      <c r="F6" s="11">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1</v>
-      </c>
-      <c r="D6" s="10">
-        <v>201</v>
-      </c>
-      <c r="E6" s="10">
-        <v>3</v>
-      </c>
-      <c r="F6" s="10">
-        <v>32</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" s="11">
-        <v>1846</v>
-      </c>
-      <c r="I6" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="10">
+      <c r="A7" s="11">
         <v>301</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1</v>
-      </c>
-      <c r="D7" s="10">
+      <c r="C7" s="11">
+        <v>1</v>
+      </c>
+      <c r="D7" s="11">
         <v>301</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="11">
         <v>3</v>
       </c>
-      <c r="F7" s="10">
-        <v>34</v>
-      </c>
-      <c r="G7" s="11" t="s">
+      <c r="F7" s="11">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1305</v>
+      </c>
+      <c r="I7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A8" s="11">
+        <v>401</v>
+      </c>
+      <c r="C8" s="11">
+        <v>1</v>
+      </c>
+      <c r="D8" s="11">
+        <v>401</v>
+      </c>
+      <c r="E8" s="11">
+        <v>3</v>
+      </c>
+      <c r="F8" s="11">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="10" t="s">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="12">
-        <v>401</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="12">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12">
-        <v>401</v>
-      </c>
-      <c r="E8" s="12">
+    <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="11">
+        <v>501</v>
+      </c>
+      <c r="C9" s="11">
+        <v>2</v>
+      </c>
+      <c r="D9" s="11">
+        <v>501</v>
+      </c>
+      <c r="E9" s="11">
         <v>3</v>
       </c>
-      <c r="F8" s="13">
-        <v>36</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="F9" s="11">
+        <v>16</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="4" t="s">
+      <c r="H9" s="3">
+        <v>1503</v>
+      </c>
+      <c r="I9" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="9" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="12">
-        <v>402</v>
-      </c>
-      <c r="B9" s="12" t="s">
+    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A10" s="11">
+        <v>601</v>
+      </c>
+      <c r="C10" s="11">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11">
+        <v>601</v>
+      </c>
+      <c r="E10" s="11">
+        <v>3</v>
+      </c>
+      <c r="F10" s="11">
+        <v>18</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="12">
-        <v>2</v>
-      </c>
-      <c r="D9" s="12">
-        <v>402</v>
-      </c>
-      <c r="E9" s="14">
-        <v>3</v>
-      </c>
-      <c r="F9" s="14">
-        <v>9999</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="H10" s="3">
+        <v>1606</v>
+      </c>
+      <c r="I10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="11" t="s">
         <v>32</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="12">
-        <v>403</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="12">
-        <v>1</v>
-      </c>
-      <c r="D10" s="12">
-        <v>403</v>
-      </c>
-      <c r="E10" s="12">
-        <v>3</v>
-      </c>
-      <c r="F10" s="13">
-        <v>40</v>
-      </c>
-      <c r="G10" s="4">
-        <v>1211</v>
-      </c>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="15">
-        <v>501</v>
-      </c>
-      <c r="B11" s="15" t="s">
+      <c r="A11" s="11">
+        <v>701</v>
+      </c>
+      <c r="C11" s="11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11">
+        <v>701</v>
+      </c>
+      <c r="E11" s="11">
+        <v>3</v>
+      </c>
+      <c r="F11" s="11">
+        <v>20</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1708</v>
+      </c>
+      <c r="I11" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A12" s="11">
+        <v>801</v>
+      </c>
+      <c r="C12" s="11">
+        <v>1</v>
+      </c>
+      <c r="D12" s="11">
+        <v>801</v>
+      </c>
+      <c r="E12" s="11">
+        <v>3</v>
+      </c>
+      <c r="F12" s="11">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A13" s="11">
+        <v>901</v>
+      </c>
+      <c r="C13" s="11">
+        <v>2</v>
+      </c>
+      <c r="D13" s="11">
+        <v>901</v>
+      </c>
+      <c r="E13" s="11">
+        <v>3</v>
+      </c>
+      <c r="F13" s="11">
         <v>24</v>
       </c>
-      <c r="C11" s="15">
-        <v>1</v>
-      </c>
-      <c r="D11" s="15">
-        <v>501</v>
-      </c>
-      <c r="E11" s="15">
+      <c r="G13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="11">
+        <v>1001</v>
+      </c>
+      <c r="C14" s="11">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11">
+        <v>1001</v>
+      </c>
+      <c r="E14" s="11">
         <v>3</v>
       </c>
-      <c r="F11" s="13">
-        <v>42</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="12">
-        <v>1001</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="12">
-        <v>1001</v>
-      </c>
-      <c r="E12" s="12">
-        <v>3</v>
-      </c>
-      <c r="F12" s="13">
-        <v>44</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="12">
-        <v>1002</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="12">
-        <v>2</v>
-      </c>
-      <c r="D13" s="12">
-        <v>1002</v>
-      </c>
-      <c r="E13" s="14">
-        <v>3</v>
-      </c>
-      <c r="F13" s="14">
-        <v>9999</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" s="12" t="s">
+      <c r="F14" s="11">
+        <v>26</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="12">
-        <v>1003</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C14" s="12">
-        <v>1</v>
-      </c>
-      <c r="D14" s="12">
-        <v>1003</v>
-      </c>
-      <c r="E14" s="12">
-        <v>3</v>
-      </c>
-      <c r="F14" s="13">
-        <v>48</v>
-      </c>
-      <c r="G14" s="4">
-        <v>1420</v>
-      </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" s="12" t="s">
-        <v>37</v>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="11" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="15">
-        <v>1011</v>
-      </c>
-      <c r="B15" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1011</v>
-      </c>
-      <c r="E15" s="15">
+      <c r="A15" s="11">
+        <v>1101</v>
+      </c>
+      <c r="C15" s="11">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11">
+        <v>1101</v>
+      </c>
+      <c r="E15" s="11">
         <v>3</v>
       </c>
-      <c r="F15" s="13">
-        <v>50</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="I15" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="15" t="s">
+      <c r="F15" s="11">
+        <v>28</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="I15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="11" t="s">
+        <v>42</v>
+      </c>
     </row>
-    <row r="16" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="12">
-        <v>1021</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C16" s="12">
-        <v>1</v>
-      </c>
-      <c r="D16" s="12">
-        <v>1021</v>
-      </c>
-      <c r="E16" s="12">
-        <v>3</v>
-      </c>
-      <c r="F16" s="13">
-        <v>52</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" s="5" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A17" s="12">
-        <v>1022</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="12">
-        <v>2</v>
-      </c>
-      <c r="D17" s="12">
-        <v>1022</v>
-      </c>
-      <c r="E17" s="14">
-        <v>3</v>
-      </c>
-      <c r="F17" s="14">
-        <v>9999</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="12" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="15">
-        <v>1031</v>
-      </c>
-      <c r="B18" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C18" s="15">
-        <v>1</v>
-      </c>
-      <c r="D18" s="15">
-        <v>1031</v>
-      </c>
-      <c r="E18" s="15">
-        <v>3</v>
-      </c>
-      <c r="F18" s="13">
-        <v>56</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I18" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" s="15" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" s="4" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A19" s="12">
-        <v>1041</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C19" s="12">
-        <v>1</v>
-      </c>
-      <c r="D19" s="12">
-        <v>1041</v>
-      </c>
-      <c r="E19" s="12">
-        <v>3</v>
-      </c>
-      <c r="F19" s="13">
-        <v>58</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="1:11">
-      <c r="A20" s="15">
-        <v>1051</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="15">
-        <v>1</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1051</v>
-      </c>
-      <c r="E20" s="15">
-        <v>3</v>
-      </c>
-      <c r="F20" s="13">
-        <v>60</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I20" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="J20" s="15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" s="6" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A21" s="16">
-        <v>1061</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C21" s="16">
-        <v>1</v>
-      </c>
-      <c r="D21" s="16">
-        <v>1061</v>
-      </c>
-      <c r="E21" s="16">
-        <v>3</v>
-      </c>
-      <c r="F21" s="16">
-        <v>9999</v>
-      </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J21" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="22" s="6" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A22" s="16">
-        <v>1071</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C22" s="16">
-        <v>1</v>
-      </c>
-      <c r="D22" s="16">
-        <v>1071</v>
-      </c>
-      <c r="E22" s="16">
-        <v>3</v>
-      </c>
-      <c r="F22" s="16">
-        <v>9999</v>
-      </c>
-      <c r="I22" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="1:11">
-      <c r="K29" s="1"/>
+    <row r="22" customHeight="1" spans="11:11">
+      <c r="K22" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A21 A23:A1048576">
+  <conditionalFormatting sqref="A$1:A$1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -246,10 +246,10 @@
     <t>建筑-愤怒的小鸟-升级1次</t>
   </si>
   <si>
-    <t>1301_1302_1303_1304_1305_1306</t>
-  </si>
-  <si>
-    <t>建筑-愤怒的小鸟-SLOT</t>
+    <t>1301_1302_1303_1304_1305</t>
+  </si>
+  <si>
+    <t>游戏首次-愤怒的小鸟-SLOT</t>
   </si>
   <si>
     <t>1401_1402_1403_1404_1405_1406</t>
@@ -261,10 +261,10 @@
     <t>1501_1502_1503_1504</t>
   </si>
   <si>
-    <t>建筑-愤怒的小鸟-SLOT2</t>
-  </si>
-  <si>
-    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612</t>
+    <t>游戏再次-愤怒的小鸟-SLOT2</t>
+  </si>
+  <si>
+    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612_1613_1614</t>
   </si>
   <si>
     <t>雇员-抽卡-升级-升星</t>
@@ -276,19 +276,19 @@
     <t>游客-抽卡-升星</t>
   </si>
   <si>
-    <t>1801_1802_1803_1804_1805_1806_1807</t>
+    <t>1801_1802_1803_1804_1805_1806_1807_1808_1809</t>
   </si>
   <si>
     <t>建筑-象财神-升级</t>
   </si>
   <si>
-    <t>1901_1902_1903_1904</t>
-  </si>
-  <si>
-    <t>赛季-界面</t>
-  </si>
-  <si>
-    <t>2001_2002_2003_2004_2005_2006_2007_2008</t>
+    <t>1901_1902_1903_1904_1905</t>
+  </si>
+  <si>
+    <t>赛季-SLOT游戏</t>
+  </si>
+  <si>
+    <t>2001_2002_2003_2004_2005_2006_2007</t>
   </si>
   <si>
     <t>赛季-斗仙牌</t>
@@ -1618,7 +1618,7 @@
         <v>31</v>
       </c>
       <c r="H10" s="3">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="I10" s="3" t="b">
         <v>1</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1500,7 +1500,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="11">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
@@ -1527,7 +1527,7 @@
         <v>3</v>
       </c>
       <c r="F7" s="11">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>25</v>
@@ -1556,7 +1556,7 @@
         <v>3</v>
       </c>
       <c r="F8" s="11">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>27</v>
@@ -1583,7 +1583,7 @@
         <v>3</v>
       </c>
       <c r="F9" s="11">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>29</v>
@@ -1612,7 +1612,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="11">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>31</v>
@@ -1641,7 +1641,7 @@
         <v>3</v>
       </c>
       <c r="F11" s="11">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
@@ -1670,7 +1670,7 @@
         <v>3</v>
       </c>
       <c r="F12" s="11">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>35</v>
@@ -1697,7 +1697,7 @@
         <v>3</v>
       </c>
       <c r="F13" s="11">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>37</v>
@@ -1724,7 +1724,7 @@
         <v>3</v>
       </c>
       <c r="F14" s="11">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>39</v>
@@ -1751,7 +1751,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="11">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>41</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -110,7 +110,8 @@
 6. 获得指定道具ID触发
 7. 功能解锁触发(回到经营大厅 填写功能ID，GameFunction.xlsx 表中ID )
 8.  引导组触发(填写的引导组完成后触发) 
-9. 功能界面首次打开触发</t>
+9. 功能界面首次打开触发
+10. 第一次打开界面触发引导(参数：10000 斗仙牌 )</t>
         </r>
       </text>
     </comment>
@@ -1078,7 +1079,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18213070" y="2770505"/>
+          <a:off x="18673445" y="2770505"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1353,7 +1354,7 @@
     <col min="3" max="3" width="10.75" style="3" customWidth="1"/>
     <col min="4" max="4" width="13.875" style="3" customWidth="1"/>
     <col min="5" max="5" width="11.875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.2916666666667" style="3" customWidth="1"/>
     <col min="7" max="7" width="83.125" style="3" customWidth="1"/>
     <col min="8" max="9" width="20.2833333333333" style="3" customWidth="1"/>
     <col min="10" max="10" width="39.5" style="3" customWidth="1"/>
@@ -1721,10 +1722,10 @@
         <v>1001</v>
       </c>
       <c r="E14" s="11">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F14" s="11">
-        <v>46</v>
+        <v>10000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>39</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -103,7 +103,7 @@
           <t xml:space="preserve">
 必填写项：
 1. 创建新号-首次进入经营大厅
-2. 任务ID触发(领取任务奖励后且回到了经营大厅)
+2. 任务ID触发(完成任务并领取奖励 )
 3. 经营等级触发(回到经营大厅)
 4. 角色等级触发(回到经营大厅)
 5. 道具不足触发(道具不足)
@@ -111,7 +111,7 @@
 7. 功能解锁触发(回到经营大厅 填写功能ID，GameFunction.xlsx 表中ID )
 8.  引导组触发(填写的引导组完成后触发) 
 9. 功能界面首次打开触发
-10. 第一次打开界面触发引导(参数：10000 斗仙牌 )</t>
+10. 第一次打开界面触发引导(参数：10000 斗仙牌 ) //已研发 </t>
         </r>
       </text>
     </comment>
@@ -235,7 +235,7 @@
     <t>isOpen</t>
   </si>
   <si>
-    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012</t>
+    <t>1001_1002_1003_1004_1005_1006_1007_1008_1009_1010_1011_1012_1013</t>
   </si>
   <si>
     <t>初入游戏-创建新号到经营大厅</t>
@@ -265,25 +265,25 @@
     <t>游戏再次-愤怒的小鸟-SLOT2</t>
   </si>
   <si>
-    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612_1613_1614</t>
+    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612</t>
   </si>
   <si>
     <t>雇员-抽卡-升级-升星</t>
   </si>
   <si>
-    <t>1701_1702_1703_1704_1705_1706_1707_1708_1709_1710_1711_1712</t>
+    <t>1701_1702_1703_1704_1705_1706_1707_1708_1709_1710_1711</t>
   </si>
   <si>
     <t>游客-抽卡-升星</t>
   </si>
   <si>
-    <t>1801_1802_1803_1804_1805_1806_1807_1808_1809</t>
+    <t>1801_1802_1803_1804_1805_1806_1807</t>
   </si>
   <si>
     <t>建筑-象财神-升级</t>
   </si>
   <si>
-    <t>1901_1902_1903_1904_1905</t>
+    <t>1901_1902_1903</t>
   </si>
   <si>
     <t>赛季-SLOT游戏</t>
@@ -295,7 +295,7 @@
     <t>赛季-斗仙牌</t>
   </si>
   <si>
-    <t>2101_2102_2103</t>
+    <t>2101_2102</t>
   </si>
   <si>
     <t>联盟</t>
@@ -311,7 +311,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -327,6 +327,12 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -812,137 +818,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -958,6 +964,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -978,6 +987,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1363,31 +1378,31 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="5" t="s">
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1395,81 +1410,81 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="9"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="9"/>
+      <c r="J3" s="10"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="10"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="11">
+      <c r="A5" s="12">
         <v>101</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12">
         <v>101</v>
       </c>
-      <c r="E5" s="11">
-        <v>1</v>
-      </c>
-      <c r="F5" s="11"/>
+      <c r="E5" s="12">
+        <v>1</v>
+      </c>
+      <c r="F5" s="12"/>
       <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
@@ -1479,28 +1494,28 @@
       <c r="I5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="11" t="s">
+      <c r="J5" s="12" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="3" t="str">
         <f>SUBSTITUTE(G5,"_",",")</f>
-        <v>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012</v>
+        <v>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="11">
+      <c r="A6" s="12">
         <v>201</v>
       </c>
-      <c r="C6" s="11">
-        <v>1</v>
-      </c>
-      <c r="D6" s="11">
+      <c r="C6" s="12">
+        <v>1</v>
+      </c>
+      <c r="D6" s="12">
         <v>201</v>
       </c>
-      <c r="E6" s="11">
+      <c r="E6" s="12">
         <v>3</v>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <v>30</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -1510,24 +1525,24 @@
       <c r="I6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J6" s="11" t="s">
+      <c r="J6" s="12" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="11">
+      <c r="A7" s="12">
         <v>301</v>
       </c>
-      <c r="C7" s="11">
-        <v>1</v>
-      </c>
-      <c r="D7" s="11">
+      <c r="C7" s="12">
+        <v>1</v>
+      </c>
+      <c r="D7" s="12">
         <v>301</v>
       </c>
-      <c r="E7" s="11">
+      <c r="E7" s="12">
         <v>3</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="12">
         <v>32</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1539,24 +1554,24 @@
       <c r="I7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J7" s="11" t="s">
+      <c r="J7" s="12" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="11">
+      <c r="A8" s="12">
         <v>401</v>
       </c>
-      <c r="C8" s="11">
-        <v>1</v>
-      </c>
-      <c r="D8" s="11">
+      <c r="C8" s="12">
+        <v>1</v>
+      </c>
+      <c r="D8" s="12">
         <v>401</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8" s="12">
         <v>3</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="12">
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1566,24 +1581,24 @@
       <c r="I8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="11" t="s">
+      <c r="J8" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="11">
+      <c r="A9" s="12">
         <v>501</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="12">
         <v>2</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="12">
         <v>501</v>
       </c>
-      <c r="E9" s="11">
+      <c r="E9" s="12">
         <v>3</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="12">
         <v>36</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1595,24 +1610,24 @@
       <c r="I9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J9" s="11" t="s">
+      <c r="J9" s="12" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="11">
+      <c r="A10" s="12">
         <v>601</v>
       </c>
-      <c r="C10" s="11">
-        <v>1</v>
-      </c>
-      <c r="D10" s="11">
+      <c r="C10" s="12">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12">
         <v>601</v>
       </c>
-      <c r="E10" s="11">
+      <c r="E10" s="12">
         <v>3</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="12">
         <v>38</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -1624,24 +1639,24 @@
       <c r="I10" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J10" s="11" t="s">
+      <c r="J10" s="12" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="11">
+      <c r="A11" s="12">
         <v>701</v>
       </c>
-      <c r="C11" s="11">
-        <v>1</v>
-      </c>
-      <c r="D11" s="11">
+      <c r="C11" s="12">
+        <v>1</v>
+      </c>
+      <c r="D11" s="12">
         <v>701</v>
       </c>
-      <c r="E11" s="11">
+      <c r="E11" s="12">
         <v>3</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="12">
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -1653,24 +1668,24 @@
       <c r="I11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="11" t="s">
+      <c r="J11" s="12" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="11">
+      <c r="A12" s="12">
         <v>801</v>
       </c>
-      <c r="C12" s="11">
-        <v>1</v>
-      </c>
-      <c r="D12" s="11">
+      <c r="C12" s="12">
+        <v>1</v>
+      </c>
+      <c r="D12" s="12">
         <v>801</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12" s="12">
         <v>3</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="12">
         <v>42</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1680,24 +1695,24 @@
       <c r="I12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="11" t="s">
+      <c r="J12" s="12" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="11">
+      <c r="A13" s="12">
         <v>901</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="12">
         <v>2</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="12">
         <v>901</v>
       </c>
-      <c r="E13" s="11">
+      <c r="E13" s="12">
         <v>3</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="12">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -1707,51 +1722,51 @@
       <c r="I13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J13" s="11" t="s">
+      <c r="J13" s="12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="11">
+    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="13">
         <v>1001</v>
       </c>
-      <c r="C14" s="11">
-        <v>1</v>
-      </c>
-      <c r="D14" s="11">
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13">
         <v>1001</v>
       </c>
-      <c r="E14" s="11">
+      <c r="E14" s="13">
         <v>10</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="13">
         <v>10000</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" s="11" t="s">
+      <c r="H14" s="14"/>
+      <c r="I14" s="14" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="13" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="11">
+      <c r="A15" s="12">
         <v>1101</v>
       </c>
-      <c r="C15" s="11">
-        <v>1</v>
-      </c>
-      <c r="D15" s="11">
+      <c r="C15" s="12">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12">
         <v>1101</v>
       </c>
-      <c r="E15" s="11">
+      <c r="E15" s="12">
         <v>3</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="12">
         <v>48</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -1760,7 +1775,7 @@
       <c r="I15" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="12" t="s">
         <v>42</v>
       </c>
     </row>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -961,6 +961,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -990,9 +993,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1378,31 +1378,31 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="6" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1410,81 +1410,81 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="10"/>
+      <c r="J2" s="11"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="10"/>
+      <c r="J3" s="11"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="12">
+      <c r="A5" s="13">
         <v>101</v>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12">
+      <c r="C5" s="13"/>
+      <c r="D5" s="13">
         <v>101</v>
       </c>
-      <c r="E5" s="12">
-        <v>1</v>
-      </c>
-      <c r="F5" s="12"/>
+      <c r="E5" s="13">
+        <v>1</v>
+      </c>
+      <c r="F5" s="13"/>
       <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
@@ -1494,7 +1494,7 @@
       <c r="I5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="13" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="3" t="str">
@@ -1502,47 +1502,47 @@
         <v>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="12">
+    <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A6" s="14">
         <v>201</v>
       </c>
-      <c r="C6" s="12">
-        <v>1</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="C6" s="14">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14">
         <v>201</v>
       </c>
-      <c r="E6" s="12">
-        <v>3</v>
-      </c>
-      <c r="F6" s="12">
-        <v>30</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="E6" s="14">
+        <v>8</v>
+      </c>
+      <c r="F6" s="14">
+        <v>101</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="12" t="s">
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="12">
+      <c r="A7" s="13">
         <v>301</v>
       </c>
-      <c r="C7" s="12">
-        <v>1</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="C7" s="13">
+        <v>1</v>
+      </c>
+      <c r="D7" s="13">
         <v>301</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="13">
         <v>3</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="13">
         <v>32</v>
       </c>
       <c r="G7" s="3" t="s">
@@ -1554,24 +1554,24 @@
       <c r="I7" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="12">
+      <c r="A8" s="13">
         <v>401</v>
       </c>
-      <c r="C8" s="12">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="13">
         <v>401</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="13">
         <v>3</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="13">
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1581,24 +1581,24 @@
       <c r="I8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="13" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="12">
+    <row r="9" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="13">
         <v>501</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <v>2</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="13">
         <v>501</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="13">
         <v>3</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="13">
         <v>36</v>
       </c>
       <c r="G9" s="3" t="s">
@@ -1610,24 +1610,24 @@
       <c r="I9" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="13" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="12">
+    <row r="10" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A10" s="13">
         <v>601</v>
       </c>
-      <c r="C10" s="12">
-        <v>1</v>
-      </c>
-      <c r="D10" s="12">
+      <c r="C10" s="13">
+        <v>1</v>
+      </c>
+      <c r="D10" s="13">
         <v>601</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E10" s="13">
         <v>3</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="13">
         <v>38</v>
       </c>
       <c r="G10" s="3" t="s">
@@ -1639,24 +1639,24 @@
       <c r="I10" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="12">
+      <c r="A11" s="13">
         <v>701</v>
       </c>
-      <c r="C11" s="12">
-        <v>1</v>
-      </c>
-      <c r="D11" s="12">
+      <c r="C11" s="13">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13">
         <v>701</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E11" s="13">
         <v>3</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="13">
         <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
@@ -1668,114 +1668,114 @@
       <c r="I11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="12">
+    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A12" s="14">
         <v>801</v>
       </c>
-      <c r="C12" s="12">
-        <v>1</v>
-      </c>
-      <c r="D12" s="12">
+      <c r="C12" s="14">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14">
         <v>801</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E12" s="14">
+        <v>2</v>
+      </c>
+      <c r="F12" s="14">
+        <v>100020008</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A13" s="14">
+        <v>901</v>
+      </c>
+      <c r="C13" s="14">
+        <v>2</v>
+      </c>
+      <c r="D13" s="14">
+        <v>901</v>
+      </c>
+      <c r="E13" s="14">
         <v>3</v>
       </c>
-      <c r="F12" s="12">
-        <v>42</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="12" t="s">
-        <v>36</v>
+      <c r="F13" s="14">
+        <v>100020025</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="14" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="13" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="12">
-        <v>901</v>
-      </c>
-      <c r="C13" s="12">
-        <v>2</v>
-      </c>
-      <c r="D13" s="12">
-        <v>901</v>
-      </c>
-      <c r="E13" s="12">
+    <row r="14" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="14">
+        <v>1001</v>
+      </c>
+      <c r="C14" s="14">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14">
+        <v>1001</v>
+      </c>
+      <c r="E14" s="14">
+        <v>10</v>
+      </c>
+      <c r="F14" s="14">
+        <v>10000</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="14">
+        <v>1101</v>
+      </c>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1101</v>
+      </c>
+      <c r="E15" s="14">
         <v>3</v>
       </c>
-      <c r="F13" s="12">
-        <v>44</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" s="12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="13">
-        <v>1001</v>
-      </c>
-      <c r="C14" s="13">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13">
-        <v>1001</v>
-      </c>
-      <c r="E14" s="13">
-        <v>10</v>
-      </c>
-      <c r="F14" s="13">
-        <v>10000</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" s="13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="12">
-        <v>1101</v>
-      </c>
-      <c r="C15" s="12">
-        <v>1</v>
-      </c>
-      <c r="D15" s="12">
-        <v>1101</v>
-      </c>
-      <c r="E15" s="12">
-        <v>3</v>
-      </c>
-      <c r="F15" s="12">
+      <c r="F15" s="14">
         <v>48</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="12" t="s">
+      <c r="I15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="14" t="s">
         <v>42</v>
       </c>
     </row>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1522,7 +1522,7 @@
         <v>23</v>
       </c>
       <c r="H6" s="4"/>
-      <c r="I6" s="4" t="b">
+      <c r="I6" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J6" s="14" t="s">
@@ -1692,7 +1692,7 @@
         <v>35</v>
       </c>
       <c r="H12" s="4"/>
-      <c r="I12" s="4" t="b">
+      <c r="I12" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J12" s="14" t="s">
@@ -1719,7 +1719,7 @@
         <v>37</v>
       </c>
       <c r="H13" s="4"/>
-      <c r="I13" s="4" t="b">
+      <c r="I13" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J13" s="14" t="s">
@@ -1746,7 +1746,7 @@
         <v>39</v>
       </c>
       <c r="H14" s="4"/>
-      <c r="I14" s="4" t="b">
+      <c r="I14" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J14" s="14" t="s">
@@ -1772,7 +1772,7 @@
       <c r="G15" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="4" t="b">
+      <c r="I15" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J15" s="14" t="s">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -481,12 +481,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>24</v>
@@ -1552,7 +1552,7 @@
         <v>1305</v>
       </c>
       <c r="I7" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" s="13" t="s">
         <v>26</v>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8" s="13" t="s">
         <v>28</v>
@@ -1608,7 +1608,7 @@
         <v>1503</v>
       </c>
       <c r="I9" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" s="13" t="s">
         <v>30</v>
@@ -1637,7 +1637,7 @@
         <v>1608</v>
       </c>
       <c r="I10" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" s="13" t="s">
         <v>32</v>
@@ -1666,7 +1666,7 @@
         <v>1708</v>
       </c>
       <c r="I11" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" s="13" t="s">
         <v>34</v>
@@ -1683,17 +1683,17 @@
         <v>801</v>
       </c>
       <c r="E12" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="14">
-        <v>100020008</v>
+        <v>45</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>35</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" s="14" t="s">
         <v>36</v>
@@ -1710,7 +1710,7 @@
         <v>901</v>
       </c>
       <c r="E13" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F13" s="14">
         <v>100020025</v>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="14" t="s">
         <v>38</v>
@@ -1773,7 +1773,7 @@
         <v>41</v>
       </c>
       <c r="I15" s="3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J15" s="14" t="s">
         <v>42</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -271,7 +271,7 @@
     <t>雇员-抽卡-升级-升星</t>
   </si>
   <si>
-    <t>1701_1702_1703_1704_1705_1706_1707_1708_1709_1710_1711</t>
+    <t>1701_1702_1703_1704_1705_1706_1707_1708_1709_1710_1711_1712</t>
   </si>
   <si>
     <t>游客-抽卡-升星</t>
@@ -481,12 +481,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -271,16 +271,16 @@
     <t>雇员-抽卡-升级-升星</t>
   </si>
   <si>
+    <t>1801_1802_1803_1804_1805_1806_1807</t>
+  </si>
+  <si>
+    <t>建筑-象财神-升级</t>
+  </si>
+  <si>
     <t>1701_1702_1703_1704_1705_1706_1707_1708_1709_1710_1711_1712</t>
   </si>
   <si>
     <t>游客-抽卡-升星</t>
-  </si>
-  <si>
-    <t>1801_1802_1803_1804_1805_1806_1807</t>
-  </si>
-  <si>
-    <t>建筑-象财神-升级</t>
   </si>
   <si>
     <t>1901_1902_1903</t>
@@ -332,7 +332,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF00B050"/>
+      <color rgb="FFC00000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -964,10 +964,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1502,119 +1502,119 @@
         <v>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013</v>
       </c>
     </row>
-    <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="14">
+    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A6" s="13">
         <v>201</v>
       </c>
-      <c r="C6" s="14">
-        <v>1</v>
-      </c>
-      <c r="D6" s="14">
+      <c r="C6" s="13">
+        <v>1</v>
+      </c>
+      <c r="D6" s="13">
         <v>201</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="13">
         <v>8</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="13">
         <v>101</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="4"/>
+      <c r="H6" s="3"/>
       <c r="I6" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J6" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="13">
+    <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A7" s="14">
         <v>301</v>
       </c>
-      <c r="C7" s="13">
-        <v>1</v>
-      </c>
-      <c r="D7" s="13">
+      <c r="C7" s="14">
+        <v>2</v>
+      </c>
+      <c r="D7" s="14">
         <v>301</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="14">
         <v>3</v>
       </c>
-      <c r="F7" s="13">
-        <v>32</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="F7" s="14">
+        <v>40</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7" s="4">
         <v>1305</v>
       </c>
-      <c r="I7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J7" s="13" t="s">
+      <c r="I7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="13">
+    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A8" s="14">
         <v>401</v>
       </c>
-      <c r="C8" s="13">
-        <v>1</v>
-      </c>
-      <c r="D8" s="13">
+      <c r="C8" s="14">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
         <v>401</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <v>3</v>
       </c>
-      <c r="F8" s="13">
-        <v>34</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="F8" s="14">
+        <v>42</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="13" t="s">
+      <c r="H8" s="4"/>
+      <c r="I8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="13">
+      <c r="A9" s="14">
         <v>501</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="14">
         <v>2</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D9" s="14">
         <v>501</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="14">
         <v>3</v>
       </c>
-      <c r="F9" s="13">
-        <v>36</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="F9" s="14">
+        <v>45</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="4">
         <v>1503</v>
       </c>
-      <c r="I9" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="13" t="s">
+      <c r="I9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" s="5" customFormat="1" customHeight="1" spans="1:12">
+    <row r="10" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A10" s="13">
         <v>601</v>
       </c>
@@ -1625,10 +1625,10 @@
         <v>601</v>
       </c>
       <c r="E10" s="13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="13">
-        <v>38</v>
+        <v>100020007</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>31</v>
@@ -1637,145 +1637,145 @@
         <v>1608</v>
       </c>
       <c r="I10" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" s="13" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:12">
+    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A11" s="13">
-        <v>701</v>
+        <v>801</v>
       </c>
       <c r="C11" s="13">
         <v>1</v>
       </c>
       <c r="D11" s="13">
-        <v>701</v>
+        <v>801</v>
       </c>
       <c r="E11" s="13">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F11" s="13">
-        <v>40</v>
+        <v>601</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="3">
-        <v>1708</v>
-      </c>
+      <c r="H11" s="3"/>
       <c r="I11" s="3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" s="13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="12" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="14">
-        <v>801</v>
-      </c>
-      <c r="C12" s="14">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14">
-        <v>801</v>
-      </c>
-      <c r="E12" s="14">
-        <v>3</v>
-      </c>
-      <c r="F12" s="14">
-        <v>45</v>
-      </c>
-      <c r="G12" s="4" t="s">
+    <row r="12" customHeight="1" spans="1:12">
+      <c r="A12" s="13">
+        <v>701</v>
+      </c>
+      <c r="C12" s="13">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13">
+        <v>701</v>
+      </c>
+      <c r="E12" s="13">
+        <v>2</v>
+      </c>
+      <c r="F12" s="13">
+        <v>100020016</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="4"/>
+      <c r="H12" s="3">
+        <v>1709</v>
+      </c>
       <c r="I12" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="14">
+      <c r="A13" s="13">
         <v>901</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13">
+        <v>901</v>
+      </c>
+      <c r="E13" s="13">
         <v>2</v>
       </c>
-      <c r="D13" s="14">
-        <v>901</v>
-      </c>
-      <c r="E13" s="14">
-        <v>2</v>
-      </c>
-      <c r="F13" s="14">
-        <v>100020025</v>
-      </c>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="13">
+        <v>100020032</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="4"/>
+      <c r="H13" s="3"/>
       <c r="I13" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="14">
+      <c r="A14" s="13">
         <v>1001</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
-      </c>
-      <c r="D14" s="14">
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13">
         <v>1001</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="13">
         <v>10</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="13">
         <v>10000</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H14" s="4"/>
+      <c r="H14" s="3"/>
       <c r="I14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="14" t="s">
+      <c r="J14" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="14">
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="13">
         <v>1101</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="13">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13">
         <v>1101</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="13">
         <v>3</v>
       </c>
-      <c r="F15" s="14">
-        <v>48</v>
-      </c>
-      <c r="G15" s="4" t="s">
+      <c r="F15" s="13">
+        <v>12</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>41</v>
       </c>
       <c r="I15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="13" t="s">
         <v>42</v>
       </c>
     </row>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -165,6 +165,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="H1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+断线后，重新边境跳过引导的ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -311,7 +333,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -337,6 +359,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.35"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -492,7 +520,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -502,6 +530,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -818,76 +858,70 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
@@ -896,10 +930,10 @@
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
@@ -908,10 +942,10 @@
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
@@ -920,10 +954,10 @@
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
@@ -932,10 +966,10 @@
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
@@ -944,11 +978,17 @@
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -970,6 +1010,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -988,10 +1031,34 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1378,31 +1445,31 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1410,280 +1477,287 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="11"/>
+      <c r="J2" s="12"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="11"/>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>101</v>
       </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13">
+      <c r="B5" s="15"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14">
         <v>101</v>
       </c>
-      <c r="E5" s="13">
-        <v>1</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="3" t="s">
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
+      <c r="F5" s="14"/>
+      <c r="G5" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="15">
         <v>1004</v>
       </c>
-      <c r="I5" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" s="13" t="s">
+      <c r="I5" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="3" t="str">
-        <f>SUBSTITUTE(G5,"_",",")</f>
-        <v>1001,1002,1003,1004,1005,1006,1007,1008,1009,1010,1011,1012,1013</v>
+        <f>SUBSTITUTE(G12,"_",",")</f>
+        <v>1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="13">
+      <c r="A6" s="14">
         <v>201</v>
       </c>
-      <c r="C6" s="13">
-        <v>1</v>
-      </c>
-      <c r="D6" s="13">
+      <c r="B6" s="15"/>
+      <c r="C6" s="14">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14">
         <v>201</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E6" s="14">
         <v>8</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <v>101</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J6" s="13" t="s">
+      <c r="H6" s="15"/>
+      <c r="I6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="14">
+      <c r="A7" s="16">
         <v>301</v>
       </c>
-      <c r="C7" s="14">
+      <c r="B7" s="17"/>
+      <c r="C7" s="16">
         <v>2</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="16">
         <v>301</v>
       </c>
-      <c r="E7" s="14">
-        <v>3</v>
-      </c>
-      <c r="F7" s="14">
-        <v>40</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="E7" s="16">
+        <v>8</v>
+      </c>
+      <c r="F7" s="16">
+        <v>201</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="17">
         <v>1305</v>
       </c>
-      <c r="I7" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="14" t="s">
+      <c r="I7" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="14">
+      <c r="A8" s="16">
         <v>401</v>
       </c>
-      <c r="C8" s="14">
-        <v>1</v>
-      </c>
-      <c r="D8" s="14">
+      <c r="B8" s="17"/>
+      <c r="C8" s="16">
+        <v>1</v>
+      </c>
+      <c r="D8" s="16">
         <v>401</v>
       </c>
-      <c r="E8" s="14">
-        <v>3</v>
-      </c>
-      <c r="F8" s="14">
-        <v>42</v>
-      </c>
-      <c r="G8" s="4" t="s">
+      <c r="E8" s="16">
+        <v>8</v>
+      </c>
+      <c r="F8" s="16">
+        <v>301</v>
+      </c>
+      <c r="G8" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="14" t="s">
+      <c r="H8" s="17"/>
+      <c r="I8" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="16" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="14">
+      <c r="A9" s="16">
         <v>501</v>
       </c>
-      <c r="C9" s="14">
+      <c r="B9" s="18"/>
+      <c r="C9" s="16">
         <v>2</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="16">
         <v>501</v>
       </c>
-      <c r="E9" s="14">
-        <v>3</v>
-      </c>
-      <c r="F9" s="14">
-        <v>45</v>
-      </c>
-      <c r="G9" s="4" t="s">
+      <c r="E9" s="16">
+        <v>8</v>
+      </c>
+      <c r="F9" s="16">
+        <v>401</v>
+      </c>
+      <c r="G9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="17">
         <v>1503</v>
       </c>
-      <c r="I9" s="4" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="14" t="s">
+      <c r="I9" s="17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="13">
+      <c r="A10" s="19">
         <v>601</v>
       </c>
-      <c r="C10" s="13">
-        <v>1</v>
-      </c>
-      <c r="D10" s="13">
+      <c r="B10" s="20"/>
+      <c r="C10" s="19">
+        <v>1</v>
+      </c>
+      <c r="D10" s="19">
         <v>601</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E10" s="19">
         <v>2</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="19">
         <v>100020007</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10" s="21">
         <v>1608</v>
       </c>
-      <c r="I10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="13" t="s">
+      <c r="I10" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="19" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="13">
+      <c r="A11" s="19">
         <v>801</v>
       </c>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
-      <c r="D11" s="13">
+      <c r="B11" s="21"/>
+      <c r="C11" s="19">
+        <v>1</v>
+      </c>
+      <c r="D11" s="19">
         <v>801</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="19">
         <v>8</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="19">
         <v>601</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="13" t="s">
+      <c r="H11" s="21"/>
+      <c r="I11" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" s="19" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:12">
-      <c r="A12" s="13">
+      <c r="A12" s="22">
         <v>701</v>
       </c>
-      <c r="C12" s="13">
-        <v>1</v>
-      </c>
-      <c r="D12" s="13">
+      <c r="C12" s="22">
+        <v>1</v>
+      </c>
+      <c r="D12" s="22">
         <v>701</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="22">
         <v>2</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="22">
         <v>100020016</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1695,24 +1769,24 @@
       <c r="I12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="22" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="13">
+      <c r="A13" s="22">
         <v>901</v>
       </c>
-      <c r="C13" s="13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="13">
+      <c r="C13" s="22">
+        <v>1</v>
+      </c>
+      <c r="D13" s="22">
         <v>901</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="22">
         <v>2</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="22">
         <v>100020032</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -1722,24 +1796,24 @@
       <c r="I13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J13" s="13" t="s">
+      <c r="J13" s="22" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="13">
+      <c r="A14" s="22">
         <v>1001</v>
       </c>
-      <c r="C14" s="13">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13">
+      <c r="C14" s="22">
+        <v>1</v>
+      </c>
+      <c r="D14" s="22">
         <v>1001</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="22">
         <v>10</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="22">
         <v>10000</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1749,33 +1823,33 @@
       <c r="I14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="13" t="s">
+      <c r="J14" s="22" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="13">
+    <row r="15" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="23">
         <v>1101</v>
       </c>
-      <c r="C15" s="13">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="23">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
         <v>1101</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="23">
         <v>3</v>
       </c>
-      <c r="F15" s="13">
-        <v>12</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="F15" s="23">
+        <v>999</v>
+      </c>
+      <c r="G15" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="13" t="s">
+      <c r="I15" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="23" t="s">
         <v>42</v>
       </c>
     </row>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -287,7 +287,7 @@
     <t>游戏再次-愤怒的小鸟-SLOT2</t>
   </si>
   <si>
-    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611_1612</t>
+    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611</t>
   </si>
   <si>
     <t>雇员-抽卡-升级-升星</t>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1707,7 +1707,7 @@
         <v>31</v>
       </c>
       <c r="H10" s="21">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="I10" s="21" t="b">
         <v>1</v>
@@ -1737,7 +1737,7 @@
         <v>33</v>
       </c>
       <c r="H11" s="21"/>
-      <c r="I11" s="21" t="b">
+      <c r="I11" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J11" s="19" t="s">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -263,7 +263,7 @@
     <t>初入游戏-创建新号到经营大厅</t>
   </si>
   <si>
-    <t>1201_1202_1203</t>
+    <t>1201_1202_1203_1204</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟-升级1次</t>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>序号</t>
   </si>
@@ -321,6 +321,12 @@
   </si>
   <si>
     <t>联盟</t>
+  </si>
+  <si>
+    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2211_2212_2213_2214</t>
+  </si>
+  <si>
+    <t>建筑-愤怒的小鸟</t>
   </si>
 </sst>
 </file>
@@ -333,7 +339,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,13 +360,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0" tint="-0.35"/>
+      <color theme="0" tint="-0.15"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -520,7 +520,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -535,13 +535,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
+        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -858,52 +852,55 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
@@ -918,77 +915,74 @@
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1010,9 +1004,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1031,35 +1022,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1445,31 +1415,31 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1477,92 +1447,92 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="7"/>
+      <c r="C2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="12"/>
+      <c r="J2" s="11"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="12"/>
+      <c r="J3" s="11"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
     </row>
     <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="14">
+      <c r="A5" s="13">
         <v>101</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14">
+      <c r="B5" s="3"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13">
         <v>101</v>
       </c>
-      <c r="E5" s="14">
-        <v>1</v>
-      </c>
-      <c r="F5" s="14"/>
-      <c r="G5" s="15" t="s">
+      <c r="E5" s="13">
+        <v>1</v>
+      </c>
+      <c r="F5" s="13"/>
+      <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="3">
         <v>1004</v>
       </c>
-      <c r="I5" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J5" s="14" t="s">
+      <c r="I5" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" s="13" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="3" t="str">
@@ -1570,11 +1540,11 @@
         <v>1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712</v>
       </c>
     </row>
-    <row r="6" s="3" customFormat="1" customHeight="1" spans="1:12">
+    <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
       <c r="A6" s="14">
         <v>201</v>
       </c>
-      <c r="B6" s="15"/>
+      <c r="B6" s="4"/>
       <c r="C6" s="14">
         <v>1</v>
       </c>
@@ -1582,182 +1552,182 @@
         <v>201</v>
       </c>
       <c r="E6" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F6" s="14">
-        <v>101</v>
-      </c>
-      <c r="G6" s="15" t="s">
+        <v>9999</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15" t="b">
-        <v>1</v>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4" t="b">
+        <v>0</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="16">
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A7" s="13">
         <v>301</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="16">
+      <c r="B7" s="3"/>
+      <c r="C7" s="13">
         <v>2</v>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="13">
         <v>301</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="13">
         <v>8</v>
       </c>
-      <c r="F7" s="16">
-        <v>201</v>
-      </c>
-      <c r="G7" s="17" t="s">
+      <c r="F7" s="13">
+        <v>1201</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="17">
+      <c r="H7" s="3">
         <v>1305</v>
       </c>
-      <c r="I7" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="16" t="s">
+      <c r="I7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="13" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="16">
+      <c r="A8" s="14">
         <v>401</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="16">
-        <v>1</v>
-      </c>
-      <c r="D8" s="16">
+      <c r="B8" s="4"/>
+      <c r="C8" s="14">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
         <v>401</v>
       </c>
-      <c r="E8" s="16">
-        <v>8</v>
-      </c>
-      <c r="F8" s="16">
-        <v>301</v>
-      </c>
-      <c r="G8" s="17" t="s">
+      <c r="E8" s="14">
+        <v>3</v>
+      </c>
+      <c r="F8" s="14">
+        <v>9999</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J8" s="16" t="s">
+      <c r="H8" s="4"/>
+      <c r="I8" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="16">
+      <c r="A9" s="14">
         <v>501</v>
       </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="16">
+      <c r="B9" s="5"/>
+      <c r="C9" s="14">
         <v>2</v>
       </c>
-      <c r="D9" s="16">
+      <c r="D9" s="14">
         <v>501</v>
       </c>
-      <c r="E9" s="16">
-        <v>8</v>
-      </c>
-      <c r="F9" s="16">
-        <v>401</v>
-      </c>
-      <c r="G9" s="17" t="s">
+      <c r="E9" s="14">
+        <v>3</v>
+      </c>
+      <c r="F9" s="14">
+        <v>9999</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="17">
+      <c r="H9" s="4">
         <v>1503</v>
       </c>
-      <c r="I9" s="17" t="b">
-        <v>1</v>
-      </c>
-      <c r="J9" s="16" t="s">
+      <c r="I9" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="19">
+      <c r="A10" s="13">
         <v>601</v>
       </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="19">
-        <v>1</v>
-      </c>
-      <c r="D10" s="19">
+      <c r="B10" s="6"/>
+      <c r="C10" s="13">
+        <v>1</v>
+      </c>
+      <c r="D10" s="13">
         <v>601</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="13">
         <v>2</v>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="13">
         <v>100020007</v>
       </c>
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="3">
         <v>1606</v>
       </c>
-      <c r="I10" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="19" t="s">
+      <c r="I10" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" s="13" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="19">
+      <c r="A11" s="13">
         <v>801</v>
       </c>
-      <c r="B11" s="21"/>
-      <c r="C11" s="19">
-        <v>1</v>
-      </c>
-      <c r="D11" s="19">
+      <c r="B11" s="3"/>
+      <c r="C11" s="13">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13">
         <v>801</v>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="13">
         <v>8</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="13">
         <v>601</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="21"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="13" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:12">
-      <c r="A12" s="22">
+      <c r="A12" s="13">
         <v>701</v>
       </c>
-      <c r="C12" s="22">
-        <v>1</v>
-      </c>
-      <c r="D12" s="22">
+      <c r="C12" s="13">
+        <v>1</v>
+      </c>
+      <c r="D12" s="13">
         <v>701</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="13">
         <v>2</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="13">
         <v>100020016</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1769,24 +1739,24 @@
       <c r="I12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="13" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="13" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="22">
+      <c r="A13" s="13">
         <v>901</v>
       </c>
-      <c r="C13" s="22">
-        <v>1</v>
-      </c>
-      <c r="D13" s="22">
+      <c r="C13" s="13">
+        <v>1</v>
+      </c>
+      <c r="D13" s="13">
         <v>901</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="13">
         <v>2</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="13">
         <v>100020032</v>
       </c>
       <c r="G13" s="3" t="s">
@@ -1796,24 +1766,24 @@
       <c r="I13" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J13" s="22" t="s">
+      <c r="J13" s="13" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="22">
+      <c r="A14" s="13">
         <v>1001</v>
       </c>
-      <c r="C14" s="22">
-        <v>1</v>
-      </c>
-      <c r="D14" s="22">
+      <c r="C14" s="13">
+        <v>1</v>
+      </c>
+      <c r="D14" s="13">
         <v>1001</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="13">
         <v>10</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="13">
         <v>10000</v>
       </c>
       <c r="G14" s="3" t="s">
@@ -1823,34 +1793,62 @@
       <c r="I14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J14" s="22" t="s">
+      <c r="J14" s="13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="23">
+    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="13">
         <v>1101</v>
       </c>
-      <c r="C15" s="23">
-        <v>1</v>
-      </c>
-      <c r="D15" s="23">
+      <c r="C15" s="13">
+        <v>1</v>
+      </c>
+      <c r="D15" s="13">
         <v>1101</v>
       </c>
-      <c r="E15" s="23">
+      <c r="E15" s="13">
         <v>3</v>
       </c>
-      <c r="F15" s="23">
-        <v>999</v>
-      </c>
-      <c r="G15" s="7" t="s">
+      <c r="F15" s="13">
+        <v>15</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I15" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J15" s="23" t="s">
+      <c r="I15" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="13" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:12">
+      <c r="A16" s="15">
+        <v>1201</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15">
+        <v>1201</v>
+      </c>
+      <c r="E16" s="15">
+        <v>8</v>
+      </c>
+      <c r="F16" s="15">
+        <v>101</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="15">
+        <v>2205</v>
+      </c>
+      <c r="I16" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="15" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="22" customHeight="1" spans="11:11">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -269,6 +269,12 @@
     <t>建筑-愤怒的小鸟-升级1次</t>
   </si>
   <si>
+    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2211_2212_2213_2214</t>
+  </si>
+  <si>
+    <t>建筑-愤怒的小鸟</t>
+  </si>
+  <si>
     <t>1301_1302_1303_1304_1305</t>
   </si>
   <si>
@@ -321,12 +327,6 @@
   </si>
   <si>
     <t>联盟</t>
-  </si>
-  <si>
-    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2211_2212_2213_2214</t>
-  </si>
-  <si>
-    <t>建筑-愤怒的小鸟</t>
   </si>
 </sst>
 </file>
@@ -1107,13 +1107,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>29845</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>230505</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>694055</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>194945</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1131,7 +1131,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18673445" y="2770505"/>
+          <a:off x="18673445" y="3024505"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1536,7 +1536,7 @@
         <v>22</v>
       </c>
       <c r="L5" s="3" t="str">
-        <f>SUBSTITUTE(G12,"_",",")</f>
+        <f>SUBSTITUTE(G13,"_",",")</f>
         <v>1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712</v>
       </c>
     </row>
@@ -1568,74 +1568,76 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A7" s="13">
+    <row r="7" customHeight="1" spans="1:12">
+      <c r="A7" s="15">
+        <v>1201</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15">
+        <v>1</v>
+      </c>
+      <c r="D7" s="15">
+        <v>1201</v>
+      </c>
+      <c r="E7" s="15">
+        <v>8</v>
+      </c>
+      <c r="F7" s="15">
+        <v>101</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="15">
+        <v>2205</v>
+      </c>
+      <c r="I7" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A8" s="13">
         <v>301</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="13">
+      <c r="B8" s="3"/>
+      <c r="C8" s="13">
         <v>2</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D8" s="13">
         <v>301</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E8" s="13">
         <v>8</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F8" s="13">
         <v>1201</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" s="3">
+      <c r="G8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="3">
         <v>1305</v>
       </c>
-      <c r="I7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>26</v>
+      <c r="I8" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" s="13" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="8" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="14">
+    <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="14">
         <v>401</v>
       </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="14">
-        <v>1</v>
-      </c>
-      <c r="D8" s="14">
+      <c r="B9" s="4"/>
+      <c r="C9" s="14">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14">
         <v>401</v>
-      </c>
-      <c r="E8" s="14">
-        <v>3</v>
-      </c>
-      <c r="F8" s="14">
-        <v>9999</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="14">
-        <v>501</v>
-      </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="14">
-        <v>2</v>
-      </c>
-      <c r="D9" s="14">
-        <v>501</v>
       </c>
       <c r="E9" s="14">
         <v>3</v>
@@ -1646,9 +1648,7 @@
       <c r="G9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="H9" s="4">
-        <v>1503</v>
-      </c>
+      <c r="H9" s="4"/>
       <c r="I9" s="4" t="b">
         <v>0</v>
       </c>
@@ -1656,57 +1656,59 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="13">
+    <row r="10" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A10" s="14">
+        <v>501</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="14">
+        <v>2</v>
+      </c>
+      <c r="D10" s="14">
+        <v>501</v>
+      </c>
+      <c r="E10" s="14">
+        <v>3</v>
+      </c>
+      <c r="F10" s="14">
+        <v>9999</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="4">
+        <v>1503</v>
+      </c>
+      <c r="I10" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" s="6" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A11" s="13">
         <v>601</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="13">
-        <v>1</v>
-      </c>
-      <c r="D10" s="13">
+      <c r="B11" s="6"/>
+      <c r="C11" s="13">
+        <v>1</v>
+      </c>
+      <c r="D11" s="13">
         <v>601</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E11" s="13">
         <v>2</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F11" s="13">
         <v>100020007</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H10" s="3">
-        <v>1606</v>
-      </c>
-      <c r="I10" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J10" s="13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="13">
-        <v>801</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
-      <c r="D11" s="13">
-        <v>801</v>
-      </c>
-      <c r="E11" s="13">
-        <v>8</v>
-      </c>
-      <c r="F11" s="13">
-        <v>601</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="3"/>
+      <c r="H11" s="3">
+        <v>1606</v>
+      </c>
       <c r="I11" s="3" t="b">
         <v>1</v>
       </c>
@@ -1714,28 +1716,27 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:12">
+    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
       <c r="A12" s="13">
-        <v>701</v>
-      </c>
+        <v>801</v>
+      </c>
+      <c r="B12" s="3"/>
       <c r="C12" s="13">
         <v>1</v>
       </c>
       <c r="D12" s="13">
-        <v>701</v>
+        <v>801</v>
       </c>
       <c r="E12" s="13">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F12" s="13">
-        <v>100020016</v>
+        <v>601</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="3">
-        <v>1709</v>
-      </c>
+      <c r="H12" s="3"/>
       <c r="I12" s="3" t="b">
         <v>1</v>
       </c>
@@ -1743,26 +1744,28 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" s="6" customFormat="1" customHeight="1" spans="1:12">
+    <row r="13" customHeight="1" spans="1:12">
       <c r="A13" s="13">
-        <v>901</v>
+        <v>701</v>
       </c>
       <c r="C13" s="13">
         <v>1</v>
       </c>
       <c r="D13" s="13">
-        <v>901</v>
+        <v>701</v>
       </c>
       <c r="E13" s="13">
         <v>2</v>
       </c>
       <c r="F13" s="13">
-        <v>100020032</v>
+        <v>100020016</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H13" s="3"/>
+      <c r="H13" s="3">
+        <v>1709</v>
+      </c>
       <c r="I13" s="3" t="b">
         <v>1</v>
       </c>
@@ -1772,19 +1775,19 @@
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A14" s="13">
-        <v>1001</v>
+        <v>901</v>
       </c>
       <c r="C14" s="13">
         <v>1</v>
       </c>
       <c r="D14" s="13">
-        <v>1001</v>
+        <v>901</v>
       </c>
       <c r="E14" s="13">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F14" s="13">
-        <v>10000</v>
+        <v>100020032</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>39</v>
@@ -1797,25 +1800,26 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" s="3" customFormat="1" customHeight="1" spans="1:12">
+    <row r="15" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A15" s="13">
-        <v>1101</v>
+        <v>1001</v>
       </c>
       <c r="C15" s="13">
         <v>1</v>
       </c>
       <c r="D15" s="13">
-        <v>1101</v>
+        <v>1001</v>
       </c>
       <c r="E15" s="13">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="F15" s="13">
-        <v>15</v>
+        <v>10000</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="H15" s="3"/>
       <c r="I15" s="3" t="b">
         <v>1</v>
       </c>
@@ -1823,31 +1827,29 @@
         <v>42</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="1:12">
-      <c r="A16" s="15">
-        <v>1201</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15">
-        <v>1201</v>
-      </c>
-      <c r="E16" s="15">
-        <v>8</v>
-      </c>
-      <c r="F16" s="15">
-        <v>101</v>
-      </c>
-      <c r="G16" s="15" t="s">
+    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A16" s="13">
+        <v>1101</v>
+      </c>
+      <c r="C16" s="13">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13">
+        <v>1101</v>
+      </c>
+      <c r="E16" s="13">
+        <v>3</v>
+      </c>
+      <c r="F16" s="13">
+        <v>15</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H16" s="15">
-        <v>2205</v>
-      </c>
-      <c r="I16" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" s="15" t="s">
+      <c r="I16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="13" t="s">
         <v>44</v>
       </c>
     </row>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -269,7 +269,7 @@
     <t>建筑-愤怒的小鸟-升级1次</t>
   </si>
   <si>
-    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2211_2212_2213_2214</t>
+    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2212_2213_2214_2215</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟</t>
@@ -1589,7 +1589,7 @@
         <v>25</v>
       </c>
       <c r="H7" s="15">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="I7" s="15" t="b">
         <v>1</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>序号</t>
   </si>
@@ -269,7 +269,10 @@
     <t>建筑-愤怒的小鸟-升级1次</t>
   </si>
   <si>
-    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2212_2213_2214_2215</t>
+    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2213_2214_2215</t>
+  </si>
+  <si>
+    <t>2206_2212</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟</t>
@@ -311,7 +314,7 @@
     <t>游客-抽卡-升星</t>
   </si>
   <si>
-    <t>1901_1902_1903</t>
+    <t>1901_1902_1903_1904_1905</t>
   </si>
   <si>
     <t>赛季-SLOT游戏</t>
@@ -327,6 +330,12 @@
   </si>
   <si>
     <t>联盟</t>
+  </si>
+  <si>
+    <t>2301_2302_2303</t>
+  </si>
+  <si>
+    <t>在线购买资源</t>
   </si>
 </sst>
 </file>
@@ -982,7 +991,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1029,6 +1038,12 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1588,14 +1603,14 @@
       <c r="G7" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="15">
-        <v>2206</v>
+      <c r="H7" s="15" t="s">
+        <v>26</v>
       </c>
       <c r="I7" s="15" t="b">
         <v>1</v>
       </c>
       <c r="J7" s="15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
@@ -1616,7 +1631,7 @@
         <v>1201</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8" s="3">
         <v>1305</v>
@@ -1625,7 +1640,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
@@ -1646,14 +1661,14 @@
         <v>9999</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4" t="b">
         <v>0</v>
       </c>
       <c r="J9" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" s="5" customFormat="1" customHeight="1" spans="1:12">
@@ -1674,7 +1689,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H10" s="4">
         <v>1503</v>
@@ -1683,7 +1698,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -1704,7 +1719,7 @@
         <v>100020007</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11" s="3">
         <v>1606</v>
@@ -1713,7 +1728,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
@@ -1734,14 +1749,14 @@
         <v>601</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:12">
@@ -1761,7 +1776,7 @@
         <v>100020016</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H13" s="3">
         <v>1709</v>
@@ -1770,34 +1785,35 @@
         <v>1</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="13">
+      <c r="A14" s="16">
         <v>901</v>
       </c>
-      <c r="C14" s="13">
-        <v>1</v>
-      </c>
-      <c r="D14" s="13">
+      <c r="B14" s="17"/>
+      <c r="C14" s="16">
+        <v>1</v>
+      </c>
+      <c r="D14" s="16">
         <v>901</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="16">
         <v>2</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="16">
         <v>100020032</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" s="13" t="s">
+      <c r="G14" s="15" t="s">
         <v>40</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -1817,14 +1833,14 @@
         <v>10000</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" customHeight="1" spans="1:12">
@@ -1844,16 +1860,44 @@
         <v>15</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I16" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="22" customHeight="1" spans="11:11">
+    <row r="17" customHeight="1" spans="1:11">
+      <c r="A17" s="15">
+        <v>1301</v>
+      </c>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15">
+        <v>1</v>
+      </c>
+      <c r="D17" s="15">
+        <v>1301</v>
+      </c>
+      <c r="E17" s="15">
+        <v>2</v>
+      </c>
+      <c r="F17" s="15">
+        <v>100020005</v>
+      </c>
+      <c r="G17" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="1:11">
       <c r="K22" s="1"/>
     </row>
   </sheetData>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -348,7 +348,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -370,6 +370,12 @@
     <font>
       <sz val="11"/>
       <color theme="0" tint="-0.15"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.25"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -861,137 +867,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1013,6 +1019,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1039,6 +1048,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1430,31 +1442,31 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
+      <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1462,82 +1474,82 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="8"/>
+      <c r="C2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="9" t="s">
+      <c r="I2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="11"/>
+      <c r="J2" s="12"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="9" t="s">
+      <c r="I3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="11"/>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="12"/>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="13">
+      <c r="A5" s="14">
         <v>101</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14">
         <v>101</v>
       </c>
-      <c r="E5" s="13">
-        <v>1</v>
-      </c>
-      <c r="F5" s="13"/>
+      <c r="E5" s="14">
+        <v>1</v>
+      </c>
+      <c r="F5" s="14"/>
       <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
@@ -1547,7 +1559,7 @@
       <c r="I5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="14" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="3" t="str">
@@ -1556,20 +1568,20 @@
       </c>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="14">
+      <c r="A6" s="15">
         <v>201</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="14">
-        <v>1</v>
-      </c>
-      <c r="D6" s="14">
+      <c r="C6" s="15">
+        <v>1</v>
+      </c>
+      <c r="D6" s="15">
         <v>201</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="15">
         <v>3</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="15">
         <v>9999</v>
       </c>
       <c r="G6" s="4" t="s">
@@ -1579,55 +1591,55 @@
       <c r="I6" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="14" t="s">
+      <c r="J6" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:12">
-      <c r="A7" s="15">
+      <c r="A7" s="16">
         <v>1201</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15">
-        <v>1</v>
-      </c>
-      <c r="D7" s="15">
+      <c r="B7" s="16"/>
+      <c r="C7" s="16">
+        <v>1</v>
+      </c>
+      <c r="D7" s="16">
         <v>1201</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="16">
         <v>8</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="16">
         <v>101</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="15" t="s">
+      <c r="I7" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="13">
+      <c r="A8" s="14">
         <v>301</v>
       </c>
       <c r="B8" s="3"/>
-      <c r="C8" s="13">
+      <c r="C8" s="14">
         <v>2</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="14">
         <v>301</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="14">
         <v>8</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <v>1201</v>
       </c>
       <c r="G8" s="3" t="s">
@@ -1639,25 +1651,25 @@
       <c r="I8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="J8" s="14" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="14">
+      <c r="A9" s="15">
         <v>401</v>
       </c>
       <c r="B9" s="4"/>
-      <c r="C9" s="14">
-        <v>1</v>
-      </c>
-      <c r="D9" s="14">
+      <c r="C9" s="15">
+        <v>1</v>
+      </c>
+      <c r="D9" s="15">
         <v>401</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="15">
         <v>3</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="15">
         <v>9999</v>
       </c>
       <c r="G9" s="4" t="s">
@@ -1667,25 +1679,25 @@
       <c r="I9" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="J9" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="10" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="14">
+      <c r="A10" s="15">
         <v>501</v>
       </c>
       <c r="B10" s="5"/>
-      <c r="C10" s="14">
+      <c r="C10" s="15">
         <v>2</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="15">
         <v>501</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E10" s="15">
         <v>3</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F10" s="15">
         <v>9999</v>
       </c>
       <c r="G10" s="4" t="s">
@@ -1697,26 +1709,26 @@
       <c r="I10" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="J10" s="15" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="13">
+      <c r="A11" s="14">
         <v>601</v>
       </c>
       <c r="B11" s="6"/>
-      <c r="C11" s="13">
-        <v>1</v>
-      </c>
-      <c r="D11" s="13">
+      <c r="C11" s="14">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14">
         <v>601</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="14">
         <v>2</v>
       </c>
-      <c r="F11" s="13">
-        <v>100020007</v>
+      <c r="F11" s="14">
+        <v>100020011</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>34</v>
@@ -1727,25 +1739,25 @@
       <c r="I11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="13">
+      <c r="A12" s="14">
         <v>801</v>
       </c>
       <c r="B12" s="3"/>
-      <c r="C12" s="13">
-        <v>1</v>
-      </c>
-      <c r="D12" s="13">
+      <c r="C12" s="14">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14">
         <v>801</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="14">
         <v>8</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <v>601</v>
       </c>
       <c r="G12" s="3" t="s">
@@ -1755,81 +1767,81 @@
       <c r="I12" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J12" s="14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="13">
+    <row r="13" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A13" s="17">
         <v>701</v>
       </c>
-      <c r="C13" s="13">
-        <v>1</v>
-      </c>
-      <c r="D13" s="13">
+      <c r="C13" s="17">
+        <v>1</v>
+      </c>
+      <c r="D13" s="17">
         <v>701</v>
       </c>
-      <c r="E13" s="13">
-        <v>2</v>
-      </c>
-      <c r="F13" s="13">
-        <v>100020016</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="E13" s="17">
+        <v>3</v>
+      </c>
+      <c r="F13" s="17">
+        <v>99999</v>
+      </c>
+      <c r="G13" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="7">
         <v>1709</v>
       </c>
-      <c r="I13" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J13" s="13" t="s">
+      <c r="I13" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="16">
+      <c r="A14" s="18">
         <v>901</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="16">
-        <v>1</v>
-      </c>
-      <c r="D14" s="16">
+      <c r="B14" s="19"/>
+      <c r="C14" s="18">
+        <v>1</v>
+      </c>
+      <c r="D14" s="18">
         <v>901</v>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="18">
         <v>2</v>
       </c>
-      <c r="F14" s="16">
-        <v>100020032</v>
-      </c>
-      <c r="G14" s="15" t="s">
+      <c r="F14" s="18">
+        <v>100020030</v>
+      </c>
+      <c r="G14" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" s="16" t="s">
+      <c r="H14" s="16"/>
+      <c r="I14" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J14" s="18" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="13">
+      <c r="A15" s="14">
         <v>1001</v>
       </c>
-      <c r="C15" s="13">
-        <v>1</v>
-      </c>
-      <c r="D15" s="13">
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
         <v>1001</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E15" s="14">
         <v>10</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <v>10000</v>
       </c>
       <c r="G15" s="3" t="s">
@@ -1839,25 +1851,25 @@
       <c r="I15" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J15" s="13" t="s">
+      <c r="J15" s="14" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="16" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="13">
+      <c r="A16" s="14">
         <v>1101</v>
       </c>
-      <c r="C16" s="13">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13">
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>1101</v>
       </c>
-      <c r="E16" s="13">
+      <c r="E16" s="14">
         <v>3</v>
       </c>
-      <c r="F16" s="13">
-        <v>15</v>
+      <c r="F16" s="14">
+        <v>8</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>44</v>
@@ -1865,35 +1877,35 @@
       <c r="I16" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="13" t="s">
+      <c r="J16" s="14" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="15">
+      <c r="A17" s="16">
         <v>1301</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15">
-        <v>1</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="B17" s="16"/>
+      <c r="C17" s="16">
+        <v>1</v>
+      </c>
+      <c r="D17" s="16">
         <v>1301</v>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="16">
         <v>2</v>
       </c>
-      <c r="F17" s="15">
-        <v>100020005</v>
-      </c>
-      <c r="G17" s="15" t="s">
+      <c r="F17" s="16">
+        <v>100020006</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="15" t="s">
+      <c r="H17" s="16"/>
+      <c r="I17" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="16" t="s">
         <v>47</v>
       </c>
     </row>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1728,7 +1728,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="14">
-        <v>100020011</v>
+        <v>100020012</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>34</v>
@@ -1815,7 +1815,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="18">
-        <v>100020030</v>
+        <v>100020034</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>40</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>序号</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>赛季-斗仙牌</t>
+  </si>
+  <si>
+    <t>联盟-触发</t>
   </si>
   <si>
     <t>2101_2102</t>
@@ -1425,7 +1428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L22"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
@@ -1855,62 +1858,90 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" s="3" customFormat="1" customHeight="1" spans="1:12">
+    <row r="16" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A16" s="14">
+        <v>1100</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1111</v>
+      </c>
+      <c r="E16" s="14">
+        <v>2</v>
+      </c>
+      <c r="F16" s="14">
+        <v>100020039</v>
+      </c>
+      <c r="G16" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A17" s="14">
         <v>1101</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
+      <c r="C17" s="14">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14">
         <v>1101</v>
       </c>
-      <c r="E16" s="14">
-        <v>3</v>
-      </c>
-      <c r="F16" s="14">
+      <c r="E17" s="14">
         <v>8</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J16" s="14" t="s">
+      <c r="F17" s="14">
+        <v>1111</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="I17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="16">
+    <row r="18" customHeight="1" spans="1:11">
+      <c r="A18" s="16">
         <v>1301</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16">
-        <v>1</v>
-      </c>
-      <c r="D17" s="16">
+      <c r="B18" s="16"/>
+      <c r="C18" s="16">
+        <v>1</v>
+      </c>
+      <c r="D18" s="16">
         <v>1301</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E18" s="16">
         <v>2</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F18" s="16">
         <v>100020006</v>
       </c>
-      <c r="G17" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="16" t="s">
+      <c r="G18" s="16" t="s">
         <v>47</v>
       </c>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="22" customHeight="1" spans="1:11">
-      <c r="K22" s="1"/>
+    <row r="23" customHeight="1" spans="1:11">
+      <c r="K23" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A$1:A$1048576">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1746,31 +1746,31 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="14">
+    <row r="12" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A12" s="17">
         <v>801</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="14">
-        <v>1</v>
-      </c>
-      <c r="D12" s="14">
+      <c r="B12" s="7"/>
+      <c r="C12" s="17">
+        <v>1</v>
+      </c>
+      <c r="D12" s="17">
         <v>801</v>
       </c>
-      <c r="E12" s="14">
-        <v>8</v>
-      </c>
-      <c r="F12" s="14">
-        <v>601</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="E12" s="17">
+        <v>3</v>
+      </c>
+      <c r="F12" s="17">
+        <v>99999</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J12" s="14" t="s">
+      <c r="H12" s="7"/>
+      <c r="I12" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" s="17" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="14">
-        <v>100020039</v>
+        <v>100020040</v>
       </c>
       <c r="G16" s="3">
         <v>2100</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1818,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="18">
-        <v>100020034</v>
+        <v>100020035</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>40</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -278,7 +278,7 @@
     <t>建筑-愤怒的小鸟</t>
   </si>
   <si>
-    <t>1301_1302_1303_1304_1305</t>
+    <t>1302_1303_1304_1305</t>
   </si>
   <si>
     <t>游戏首次-愤怒的小鸟-SLOT</t>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1924,10 +1924,10 @@
         <v>1301</v>
       </c>
       <c r="E18" s="16">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="16">
-        <v>100020006</v>
+        <v>9999999</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>47</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -103,7 +103,7 @@
           <t xml:space="preserve">
 必填写项：
 1. 创建新号-首次进入经营大厅
-2. 任务ID触发(完成任务并领取奖励 )
+2. 任务ID触发(完成任务))
 3. 经营等级触发(回到经营大厅)
 4. 角色等级触发(回到经营大厅)
 5. 道具不足触发(道具不足)

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -269,10 +269,10 @@
     <t>建筑-愤怒的小鸟-升级1次</t>
   </si>
   <si>
-    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2213_2214_2215</t>
-  </si>
-  <si>
-    <t>2206_2212</t>
+    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2213_2214_2215_2216</t>
+  </si>
+  <si>
+    <t>2206_2213</t>
   </si>
   <si>
     <t>建筑-愤怒的小鸟</t>
@@ -335,7 +335,7 @@
     <t>联盟</t>
   </si>
   <si>
-    <t>2301_2302_2303</t>
+    <t>2301_2302</t>
   </si>
   <si>
     <t>在线购买资源</t>
@@ -1731,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="14">
-        <v>100020012</v>
+        <v>100020014</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>34</v>
@@ -1818,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="18">
-        <v>100020035</v>
+        <v>100020054</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>40</v>
@@ -1873,7 +1873,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="14">
-        <v>100020040</v>
+        <v>100020063</v>
       </c>
       <c r="G16" s="3">
         <v>2100</v>
@@ -1924,10 +1924,10 @@
         <v>1301</v>
       </c>
       <c r="E18" s="16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18" s="16">
-        <v>9999999</v>
+        <v>100020006</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>47</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -269,7 +269,7 @@
     <t>建筑-愤怒的小鸟-升级1次</t>
   </si>
   <si>
-    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2213_2214_2215_2216</t>
+    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2212_2213_2214_2215_2216</t>
   </si>
   <si>
     <t>2206_2213</t>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>序号</t>
   </si>
@@ -276,9 +276,6 @@
   </si>
   <si>
     <t>建筑-愤怒的小鸟</t>
-  </si>
-  <si>
-    <t>1302_1303_1304_1305</t>
   </si>
   <si>
     <t>游戏首次-愤怒的小鸟-SLOT</t>
@@ -1645,8 +1642,8 @@
       <c r="F8" s="14">
         <v>1201</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>28</v>
+      <c r="G8" s="3">
+        <v>1302</v>
       </c>
       <c r="H8" s="3">
         <v>1305</v>
@@ -1655,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
@@ -1676,14 +1673,14 @@
         <v>9999</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4" t="b">
         <v>0</v>
       </c>
       <c r="J9" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" s="5" customFormat="1" customHeight="1" spans="1:12">
@@ -1704,7 +1701,7 @@
         <v>9999</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10" s="4">
         <v>1503</v>
@@ -1713,7 +1710,7 @@
         <v>0</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -1734,7 +1731,7 @@
         <v>100020014</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H11" s="3">
         <v>1606</v>
@@ -1743,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -1764,14 +1761,14 @@
         <v>99999</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" s="7"/>
       <c r="I12" s="4" t="b">
         <v>0</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -1791,7 +1788,7 @@
         <v>99999</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H13" s="7">
         <v>1709</v>
@@ -1800,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -1821,14 +1818,14 @@
         <v>100020054</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="16" t="b">
         <v>1</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -1848,14 +1845,14 @@
         <v>10000</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -1873,7 +1870,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="14">
-        <v>100020063</v>
+        <v>100020061</v>
       </c>
       <c r="G16" s="3">
         <v>2100</v>
@@ -1883,7 +1880,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" s="3" customFormat="1" customHeight="1" spans="1:11">
@@ -1903,13 +1900,13 @@
         <v>1111</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="I17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="14" t="s">
         <v>45</v>
-      </c>
-      <c r="I17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="14" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="18" customHeight="1" spans="1:11">
@@ -1930,14 +1927,14 @@
         <v>100020006</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H18" s="16"/>
       <c r="I18" s="16" t="b">
         <v>1</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" customHeight="1" spans="1:11">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1815,7 +1815,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="18">
-        <v>100020054</v>
+        <v>100020052</v>
       </c>
       <c r="G14" s="16" t="s">
         <v>39</v>
@@ -1870,7 +1870,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="14">
-        <v>100020061</v>
+        <v>100020059</v>
       </c>
       <c r="G16" s="3">
         <v>2100</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
   <si>
     <t>序号</t>
   </si>
@@ -269,7 +269,7 @@
     <t>建筑-愤怒的小鸟-升级1次</t>
   </si>
   <si>
-    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2212_2213_2214_2215_2216</t>
+    <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2212_2213_2214_2215_2216_2217</t>
   </si>
   <si>
     <t>2206_2213</t>
@@ -311,7 +311,10 @@
     <t>游客-抽卡-升星</t>
   </si>
   <si>
-    <t>1901_1902_1903_1904_1905</t>
+    <t>赛季-SLOT游戏-退出游戏</t>
+  </si>
+  <si>
+    <t>1902_1903_1904_1905</t>
   </si>
   <si>
     <t>赛季-SLOT游戏</t>
@@ -335,7 +338,7 @@
     <t>2301_2302</t>
   </si>
   <si>
-    <t>在线购买资源</t>
+    <t>快速获得资源</t>
   </si>
 </sst>
 </file>
@@ -1425,7 +1428,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
@@ -1815,65 +1818,65 @@
         <v>2</v>
       </c>
       <c r="F14" s="18">
-        <v>100020052</v>
-      </c>
-      <c r="G14" s="16" t="s">
-        <v>39</v>
+        <v>100020046</v>
+      </c>
+      <c r="G14" s="16">
+        <v>1901</v>
       </c>
       <c r="H14" s="16"/>
       <c r="I14" s="16" t="b">
         <v>1</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="14">
-        <v>1001</v>
-      </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1001</v>
-      </c>
-      <c r="E15" s="14">
-        <v>10</v>
-      </c>
-      <c r="F15" s="14">
-        <v>10000</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="A15" s="18">
+        <v>902</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="18">
+        <v>1</v>
+      </c>
+      <c r="D15" s="18">
+        <v>902</v>
+      </c>
+      <c r="E15" s="18">
+        <v>8</v>
+      </c>
+      <c r="F15" s="18">
+        <v>901</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="16"/>
+      <c r="I15" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" s="18" t="s">
         <v>41</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="14" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" s="6" customFormat="1" customHeight="1" spans="1:12">
       <c r="A16" s="14">
-        <v>1100</v>
-      </c>
-      <c r="B16" s="3"/>
+        <v>1001</v>
+      </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1111</v>
+        <v>1001</v>
       </c>
       <c r="E16" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="F16" s="14">
-        <v>100020059</v>
-      </c>
-      <c r="G16" s="3">
-        <v>2100</v>
+        <v>10000</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>42</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="b">
@@ -1883,62 +1886,90 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" s="3" customFormat="1" customHeight="1" spans="1:11">
+    <row r="17" s="6" customFormat="1" customHeight="1" spans="1:11">
       <c r="A17" s="14">
+        <v>1100</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>1111</v>
+      </c>
+      <c r="E17" s="14">
+        <v>2</v>
+      </c>
+      <c r="F17" s="14">
+        <v>100020059</v>
+      </c>
+      <c r="G17" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A18" s="14">
         <v>1101</v>
       </c>
-      <c r="C17" s="14">
-        <v>1</v>
-      </c>
-      <c r="D17" s="14">
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>1101</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E18" s="14">
         <v>8</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F18" s="14">
         <v>1111</v>
       </c>
-      <c r="G17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J17" s="14" t="s">
+      <c r="G18" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="I18" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" s="14" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="18" customHeight="1" spans="1:11">
-      <c r="A18" s="16">
+    <row r="19" customHeight="1" spans="1:11">
+      <c r="A19" s="16">
         <v>1301</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16">
-        <v>1</v>
-      </c>
-      <c r="D18" s="16">
+      <c r="B19" s="16"/>
+      <c r="C19" s="16">
+        <v>1</v>
+      </c>
+      <c r="D19" s="16">
         <v>1301</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E19" s="16">
         <v>2</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F19" s="16">
         <v>100020006</v>
       </c>
-      <c r="G18" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J18" s="16" t="s">
+      <c r="G19" s="16" t="s">
         <v>47</v>
       </c>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>48</v>
+      </c>
     </row>
-    <row r="23" customHeight="1" spans="1:11">
-      <c r="K23" s="1"/>
+    <row r="24" customHeight="1" spans="1:11">
+      <c r="K24" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A$1:A$1048576">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1809,7 +1809,7 @@
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="18">
         <v>901</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -1731,7 +1731,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="14">
-        <v>100020014</v>
+        <v>100020015</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>33</v>
@@ -1818,7 +1818,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="18">
-        <v>100020046</v>
+        <v>100020045</v>
       </c>
       <c r="G14" s="16">
         <v>1901</v>
@@ -1901,7 +1901,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="14">
-        <v>100020059</v>
+        <v>100020058</v>
       </c>
       <c r="G17" s="3">
         <v>2100</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
   <si>
     <t>序号</t>
   </si>
@@ -266,7 +266,7 @@
     <t>1201_1202_1203_1204</t>
   </si>
   <si>
-    <t>建筑-愤怒的小鸟-升级1次</t>
+    <t>建筑-萌宠小队-升级1次</t>
   </si>
   <si>
     <t>2201_2202_2203_2204_2205_2206_2207_2208_2209_2210_2211_2212_2213_2214_2215_2216_2217</t>
@@ -275,25 +275,34 @@
     <t>2206_2213</t>
   </si>
   <si>
-    <t>建筑-愤怒的小鸟</t>
-  </si>
-  <si>
-    <t>游戏首次-愤怒的小鸟-SLOT</t>
+    <t>建筑-萌宠小队</t>
+  </si>
+  <si>
+    <t>游戏首次-萌宠小队-SLOT</t>
+  </si>
+  <si>
+    <t>1311_1312_1313_1314</t>
+  </si>
+  <si>
+    <t>萌宠小队-SLOT-设置旋转次数</t>
   </si>
   <si>
     <t>1401_1402_1403_1404_1405_1406</t>
   </si>
   <si>
-    <t>建筑-愤怒的小鸟-升到2级</t>
+    <t>建筑-萌宠小队-升到2级</t>
   </si>
   <si>
     <t>1501_1502_1503_1504</t>
   </si>
   <si>
-    <t>游戏再次-愤怒的小鸟-SLOT2</t>
-  </si>
-  <si>
-    <t>1601_1602_1603_1604_1605_1606_1607_1608_1609_1610_1611</t>
+    <t>游戏再次-萌宠小队-SLOT2</t>
+  </si>
+  <si>
+    <t>萌宠小队-SLOT</t>
+  </si>
+  <si>
+    <t>1603_1604_1605_1606_1607_1608_1609_1610_1611</t>
   </si>
   <si>
     <t>雇员-抽卡-升级-升星</t>
@@ -339,6 +348,15 @@
   </si>
   <si>
     <t>快速获得资源</t>
+  </si>
+  <si>
+    <t>2402_2403</t>
+  </si>
+  <si>
+    <t>引导主线离开游戏</t>
+  </si>
+  <si>
+    <t>引导主线继续任务</t>
   </si>
 </sst>
 </file>
@@ -351,7 +369,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,7 +396,19 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -538,7 +568,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -548,12 +578,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -870,133 +894,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1016,13 +1040,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1049,17 +1079,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1123,6 +1147,11 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00FF0000"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1137,13 +1166,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>29845</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>230505</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>694055</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>194945</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1161,7 +1190,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18673445" y="3024505"/>
+          <a:off x="18673445" y="3532505"/>
           <a:ext cx="8998585" cy="2758440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1428,7 +1457,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L24"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultColWidth="15.625" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.875" style="3" customWidth="1"/>
@@ -1445,31 +1474,31 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="12" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1477,82 +1506,82 @@
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="12"/>
+      <c r="J2" s="14"/>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="J3" s="12"/>
+      <c r="J3" s="14"/>
     </row>
     <row r="4" s="2" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="15"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
     </row>
     <row r="5" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A5" s="14">
+      <c r="A5" s="16">
         <v>101</v>
       </c>
       <c r="B5" s="3"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16">
         <v>101</v>
       </c>
-      <c r="E5" s="14">
-        <v>1</v>
-      </c>
-      <c r="F5" s="14"/>
+      <c r="E5" s="16">
+        <v>1</v>
+      </c>
+      <c r="F5" s="16"/>
       <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
@@ -1562,29 +1591,29 @@
       <c r="I5" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="16" t="s">
         <v>22</v>
       </c>
       <c r="L5" s="3" t="str">
-        <f>SUBSTITUTE(G13,"_",",")</f>
+        <f>SUBSTITUTE(G15,"_",",")</f>
         <v>1701,1702,1703,1704,1705,1706,1707,1708,1709,1710,1711,1712</v>
       </c>
     </row>
     <row r="6" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A6" s="15">
+      <c r="A6" s="17">
         <v>201</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="15">
-        <v>1</v>
-      </c>
-      <c r="D6" s="15">
+      <c r="C6" s="17">
+        <v>1</v>
+      </c>
+      <c r="D6" s="17">
         <v>201</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="17">
         <v>3</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="17">
         <v>9999</v>
       </c>
       <c r="G6" s="4" t="s">
@@ -1594,382 +1623,485 @@
       <c r="I6" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J6" s="15" t="s">
+      <c r="J6" s="17" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="1:12">
-      <c r="A7" s="16">
+    <row r="7" s="3" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A7" s="3">
         <v>1201</v>
       </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16">
-        <v>1</v>
-      </c>
-      <c r="D7" s="16">
+      <c r="B7" s="3"/>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
         <v>1201</v>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="3">
         <v>8</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="3">
         <v>101</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="16" t="s">
+      <c r="I7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8" s="3" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A8" s="14">
-        <v>301</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="14">
+      <c r="A8" s="3">
+        <v>300</v>
+      </c>
+      <c r="C8" s="3">
         <v>2</v>
       </c>
-      <c r="D8" s="14">
-        <v>301</v>
-      </c>
-      <c r="E8" s="14">
+      <c r="D8" s="3">
+        <v>300</v>
+      </c>
+      <c r="E8" s="3">
         <v>8</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="3">
         <v>1201</v>
       </c>
       <c r="G8" s="3">
         <v>1302</v>
       </c>
-      <c r="H8" s="3">
-        <v>1305</v>
-      </c>
       <c r="I8" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="16" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="9" s="4" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A9" s="15">
+    <row r="9" s="5" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A9" s="18">
+        <v>301</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="18">
+        <v>2</v>
+      </c>
+      <c r="D9" s="18">
+        <v>301</v>
+      </c>
+      <c r="E9" s="18">
+        <v>2</v>
+      </c>
+      <c r="F9" s="18">
+        <v>100020007</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A10" s="17">
         <v>401</v>
       </c>
-      <c r="B9" s="4"/>
-      <c r="C9" s="15">
-        <v>1</v>
-      </c>
-      <c r="D9" s="15">
+      <c r="B10" s="4"/>
+      <c r="C10" s="17">
+        <v>1</v>
+      </c>
+      <c r="D10" s="17">
         <v>401</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E10" s="17">
         <v>3</v>
       </c>
-      <c r="F9" s="15">
-        <v>9999</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J9" s="15" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" s="5" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A10" s="15">
-        <v>501</v>
-      </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="15">
-        <v>2</v>
-      </c>
-      <c r="D10" s="15">
-        <v>501</v>
-      </c>
-      <c r="E10" s="15">
-        <v>3</v>
-      </c>
-      <c r="F10" s="15">
+      <c r="F10" s="17">
         <v>9999</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H10" s="4">
-        <v>1503</v>
-      </c>
+      <c r="H10" s="4"/>
       <c r="I10" s="4" t="b">
         <v>0</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="17" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A11" s="14">
+      <c r="A11" s="17">
+        <v>501</v>
+      </c>
+      <c r="B11" s="6"/>
+      <c r="C11" s="17">
+        <v>2</v>
+      </c>
+      <c r="D11" s="17">
+        <v>501</v>
+      </c>
+      <c r="E11" s="17">
+        <v>3</v>
+      </c>
+      <c r="F11" s="17">
+        <v>9999</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="H11" s="4">
+        <v>1503</v>
+      </c>
+      <c r="I11" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A12" s="16">
+        <v>600</v>
+      </c>
+      <c r="C12" s="16">
+        <v>2</v>
+      </c>
+      <c r="D12" s="16">
+        <v>600</v>
+      </c>
+      <c r="E12" s="16">
+        <v>2</v>
+      </c>
+      <c r="F12" s="16">
+        <v>100020015</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1602</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A13" s="16">
         <v>601</v>
       </c>
-      <c r="B11" s="6"/>
-      <c r="C11" s="14">
-        <v>1</v>
-      </c>
-      <c r="D11" s="14">
+      <c r="B13" s="7"/>
+      <c r="C13" s="16">
+        <v>1</v>
+      </c>
+      <c r="D13" s="16">
         <v>601</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E13" s="16">
+        <v>8</v>
+      </c>
+      <c r="F13" s="16">
+        <v>600</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1606</v>
+      </c>
+      <c r="I13" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A14" s="19">
+        <v>801</v>
+      </c>
+      <c r="B14" s="8"/>
+      <c r="C14" s="19">
+        <v>1</v>
+      </c>
+      <c r="D14" s="19">
+        <v>801</v>
+      </c>
+      <c r="E14" s="19">
+        <v>3</v>
+      </c>
+      <c r="F14" s="19">
+        <v>99999</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="8"/>
+      <c r="I14" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" s="19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" s="8" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A15" s="19">
+        <v>701</v>
+      </c>
+      <c r="C15" s="19">
+        <v>1</v>
+      </c>
+      <c r="D15" s="19">
+        <v>701</v>
+      </c>
+      <c r="E15" s="19">
+        <v>3</v>
+      </c>
+      <c r="F15" s="19">
+        <v>99999</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="8">
+        <v>1709</v>
+      </c>
+      <c r="I15" s="4" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" s="7" customFormat="1" customHeight="1" spans="1:12">
+      <c r="A16" s="16">
+        <v>901</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="16">
         <v>2</v>
       </c>
-      <c r="F11" s="14">
-        <v>100020015</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1606</v>
-      </c>
-      <c r="I11" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A12" s="17">
-        <v>801</v>
-      </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="17">
-        <v>1</v>
-      </c>
-      <c r="D12" s="17">
-        <v>801</v>
-      </c>
-      <c r="E12" s="17">
-        <v>3</v>
-      </c>
-      <c r="F12" s="17">
-        <v>99999</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" s="7" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A13" s="17">
-        <v>701</v>
-      </c>
-      <c r="C13" s="17">
-        <v>1</v>
-      </c>
-      <c r="D13" s="17">
-        <v>701</v>
-      </c>
-      <c r="E13" s="17">
-        <v>3</v>
-      </c>
-      <c r="F13" s="17">
-        <v>99999</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="7">
-        <v>1709</v>
-      </c>
-      <c r="I13" s="4" t="b">
-        <v>0</v>
-      </c>
-      <c r="J13" s="17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A14" s="18">
+      <c r="D16" s="16">
         <v>901</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="18">
+      <c r="E16" s="16">
         <v>2</v>
       </c>
-      <c r="D14" s="18">
-        <v>901</v>
-      </c>
-      <c r="E14" s="18">
-        <v>2</v>
-      </c>
-      <c r="F14" s="18">
-        <v>100020045</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="F16" s="16">
+        <v>100020042</v>
+      </c>
+      <c r="G16" s="3">
         <v>1901</v>
-      </c>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A15" s="18">
-        <v>902</v>
-      </c>
-      <c r="B15" s="19"/>
-      <c r="C15" s="18">
-        <v>1</v>
-      </c>
-      <c r="D15" s="18">
-        <v>902</v>
-      </c>
-      <c r="E15" s="18">
-        <v>8</v>
-      </c>
-      <c r="F15" s="18">
-        <v>901</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" s="6" customFormat="1" customHeight="1" spans="1:12">
-      <c r="A16" s="14">
-        <v>1001</v>
-      </c>
-      <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1001</v>
-      </c>
-      <c r="E16" s="14">
-        <v>10</v>
-      </c>
-      <c r="F16" s="14">
-        <v>10000</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J16" s="14" t="s">
+      <c r="J16" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" s="7" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A17" s="16">
+        <v>902</v>
+      </c>
+      <c r="B17" s="7"/>
+      <c r="C17" s="16">
+        <v>1</v>
+      </c>
+      <c r="D17" s="16">
+        <v>902</v>
+      </c>
+      <c r="E17" s="16">
+        <v>8</v>
+      </c>
+      <c r="F17" s="16">
+        <v>901</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="17" s="6" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A17" s="14">
-        <v>1100</v>
-      </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="14">
-        <v>2</v>
-      </c>
-      <c r="D17" s="14">
-        <v>1111</v>
-      </c>
-      <c r="E17" s="14">
-        <v>2</v>
-      </c>
-      <c r="F17" s="14">
-        <v>100020058</v>
-      </c>
-      <c r="G17" s="3">
-        <v>2100</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J17" s="14" t="s">
+      <c r="J17" s="16" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" s="3" customFormat="1" customHeight="1" spans="1:11">
-      <c r="A18" s="14">
-        <v>1101</v>
-      </c>
-      <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1101</v>
-      </c>
-      <c r="E18" s="14">
-        <v>8</v>
-      </c>
-      <c r="F18" s="14">
-        <v>1111</v>
+    <row r="18" s="7" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A18" s="16">
+        <v>1001</v>
+      </c>
+      <c r="C18" s="16">
+        <v>1</v>
+      </c>
+      <c r="D18" s="16">
+        <v>1001</v>
+      </c>
+      <c r="E18" s="16">
+        <v>10</v>
+      </c>
+      <c r="F18" s="16">
+        <v>10000</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="H18" s="3"/>
       <c r="I18" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="J18" s="14" t="s">
+      <c r="J18" s="16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="19" customHeight="1" spans="1:11">
+    <row r="19" s="7" customFormat="1" customHeight="1" spans="1:11">
       <c r="A19" s="16">
-        <v>1301</v>
-      </c>
-      <c r="B19" s="16"/>
+        <v>1100</v>
+      </c>
+      <c r="B19" s="3"/>
       <c r="C19" s="16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="16">
-        <v>1301</v>
+        <v>1111</v>
       </c>
       <c r="E19" s="16">
         <v>2</v>
       </c>
       <c r="F19" s="16">
+        <v>100020055</v>
+      </c>
+      <c r="G19" s="3">
+        <v>2100</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" s="3" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A20" s="16">
+        <v>1101</v>
+      </c>
+      <c r="C20" s="16">
+        <v>1</v>
+      </c>
+      <c r="D20" s="16">
+        <v>1101</v>
+      </c>
+      <c r="E20" s="16">
+        <v>8</v>
+      </c>
+      <c r="F20" s="16">
+        <v>1111</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I20" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" s="3" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A21" s="3">
+        <v>1301</v>
+      </c>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3">
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
+        <v>1301</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="3">
         <v>100020006</v>
       </c>
-      <c r="G19" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="1:11">
-      <c r="K24" s="1"/>
+      <c r="G21" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="22" s="9" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A22" s="9">
+        <v>1401</v>
+      </c>
+      <c r="C22" s="9">
+        <v>2</v>
+      </c>
+      <c r="D22" s="9">
+        <v>1401</v>
+      </c>
+      <c r="E22" s="9">
+        <v>2</v>
+      </c>
+      <c r="F22" s="9">
+        <v>100020004</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I22" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="23" s="9" customFormat="1" customHeight="1" spans="1:11">
+      <c r="A23" s="9">
+        <v>1402</v>
+      </c>
+      <c r="C23" s="9">
+        <v>1</v>
+      </c>
+      <c r="D23" s="9">
+        <v>1402</v>
+      </c>
+      <c r="E23" s="9">
+        <v>8</v>
+      </c>
+      <c r="F23" s="9">
+        <v>1401</v>
+      </c>
+      <c r="G23" s="9">
+        <v>2401</v>
+      </c>
+      <c r="I23" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:11">
+      <c r="K26" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A$1:A$1048576">

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -2035,7 +2035,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="3">
-        <v>100020006</v>
+        <v>100020021</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>50</v>

--- a/hall/resources/sample/Guide.xlsx
+++ b/hall/resources/sample/Guide.xlsx
@@ -192,7 +192,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>序号</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>建筑-萌宠小队</t>
+  </si>
+  <si>
+    <t>1302_1303</t>
   </si>
   <si>
     <t>游戏首次-萌宠小队-SLOT</t>
@@ -1673,14 +1676,14 @@
       <c r="F8" s="3">
         <v>1201</v>
       </c>
-      <c r="G8" s="3">
-        <v>1302</v>
+      <c r="G8" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="I8" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" s="5" customFormat="1" customHeight="1" spans="1:12">
@@ -1701,14 +1704,14 @@
         <v>100020007</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5" t="b">
         <v>1</v>
       </c>
       <c r="J9" s="18" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" s="4" customFormat="1" customHeight="1" spans="1:12">
@@ -1729,14 +1732,14 @@
         <v>9999</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4" t="b">
         <v>0</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" s="6" customFormat="1" customHeight="1" spans="1:12">
@@ -1757,7 +1760,7 @@
         <v>9999</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H11" s="4">
         <v>1503</v>
@@ -1766,7 +1769,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -1793,7 +1796,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -1814,7 +1817,7 @@
         <v>600</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H13" s="3">
         <v>1606</v>
@@ -1823,7 +1826,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" s="8" customFormat="1" customHeight="1" spans="1:12">
@@ -1844,14 +1847,14 @@
         <v>99999</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H14" s="8"/>
       <c r="I14" s="4" t="b">
         <v>0</v>
       </c>
       <c r="J14" s="19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" s="8" customFormat="1" customHeight="1" spans="1:12">
@@ -1871,7 +1874,7 @@
         <v>99999</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H15" s="8">
         <v>1709</v>
@@ -1880,7 +1883,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" s="7" customFormat="1" customHeight="1" spans="1:12">
@@ -1898,7 +1901,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="16">
-        <v>100020042</v>
+        <v>100020034</v>
       </c>
       <c r="G16" s="3">
         <v>1901</v>
@@ -1908,7 +1911,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" s="7" customFormat="1" customHeight="1" spans="1:11">
@@ -1929,14 +1932,14 @@
         <v>901</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18" s="7" customFormat="1" customHeight="1" spans="1:11">
@@ -1956,14 +1959,14 @@
         <v>10000</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" s="7" customFormat="1" customHeight="1" spans="1:11">
@@ -1981,7 +1984,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="16">
-        <v>100020055</v>
+        <v>100020045</v>
       </c>
       <c r="G19" s="3">
         <v>2100</v>
@@ -1991,7 +1994,7 @@
         <v>1</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" s="3" customFormat="1" customHeight="1" spans="1:11">
@@ -2011,13 +2014,13 @@
         <v>1111</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I20" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="1:11">
@@ -2038,14 +2041,14 @@
         <v>100020021</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="22" s="9" customFormat="1" customHeight="1" spans="1:11">
@@ -2065,13 +2068,13 @@
         <v>100020004</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I22" s="9" t="b">
         <v>1</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" s="9" customFormat="1" customHeight="1" spans="1:11">
@@ -2097,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" customHeight="1" spans="1:11">
